--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_coal_related_energy.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1158707014875028</v>
+        <v>0.1156749600845278</v>
       </c>
       <c r="C2">
-        <v>10229.1606742552</v>
+        <v>10147.50185717095</v>
       </c>
       <c r="D2">
-        <v>9733.660674255205</v>
+        <v>9754.452857170945</v>
       </c>
       <c r="E2">
-        <v>-269.4</v>
+        <v>-166.949</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>102.451</v>
       </c>
       <c r="G2">
         <v>495.5</v>
@@ -1457,28 +1457,28 @@
         <v>1477.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.1532853</v>
       </c>
       <c r="N2">
-        <v>1477.7</v>
+        <v>1472.5467147</v>
       </c>
       <c r="O2">
-        <v>295.54</v>
+        <v>294.50934294</v>
       </c>
       <c r="P2">
-        <v>1182.16</v>
+        <v>1178.03737176</v>
       </c>
       <c r="Q2">
-        <v>1435.76</v>
+        <v>1431.63737176</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1158707014875028</v>
+        <v>0.1164369293783109</v>
       </c>
       <c r="T2">
-        <v>1.083971466858168</v>
+        <v>1.092730832246921</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>286.7491151712481</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1156749600845278</v>
+        <v>0.1154792186815527</v>
       </c>
       <c r="C3">
-        <v>10147.50185717095</v>
+        <v>10065.93205907646</v>
       </c>
       <c r="D3">
-        <v>9754.452857170945</v>
+        <v>9775.334059076456</v>
       </c>
       <c r="E3">
-        <v>-166.949</v>
+        <v>-64.49799999999996</v>
       </c>
       <c r="F3">
-        <v>102.451</v>
+        <v>204.902</v>
       </c>
       <c r="G3">
         <v>495.5</v>
@@ -1539,28 +1539,28 @@
         <v>1477.7</v>
       </c>
       <c r="M3">
-        <v>5.1532853</v>
+        <v>10.3065706</v>
       </c>
       <c r="N3">
-        <v>1472.5467147</v>
+        <v>1467.3934294</v>
       </c>
       <c r="O3">
-        <v>294.50934294</v>
+        <v>293.47868588</v>
       </c>
       <c r="P3">
-        <v>1178.03737176</v>
+        <v>1173.91474352</v>
       </c>
       <c r="Q3">
-        <v>1431.63737176</v>
+        <v>1427.51474352</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1164369293783109</v>
+        <v>0.1170147129403599</v>
       </c>
       <c r="T3">
-        <v>1.092730832246921</v>
+        <v>1.101668960194628</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>286.7491151712481</v>
+        <v>143.3745575856241</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1154792186815527</v>
+        <v>0.1152834772785778</v>
       </c>
       <c r="C4">
-        <v>10065.93205907646</v>
+        <v>9984.451852882747</v>
       </c>
       <c r="D4">
-        <v>9775.334059076456</v>
+        <v>9796.304852882746</v>
       </c>
       <c r="E4">
-        <v>-64.49799999999996</v>
+        <v>37.95300000000003</v>
       </c>
       <c r="F4">
-        <v>204.902</v>
+        <v>307.353</v>
       </c>
       <c r="G4">
         <v>495.5</v>
@@ -1621,28 +1621,28 @@
         <v>1477.7</v>
       </c>
       <c r="M4">
-        <v>10.3065706</v>
+        <v>15.4598559</v>
       </c>
       <c r="N4">
-        <v>1467.3934294</v>
+        <v>1462.2401441</v>
       </c>
       <c r="O4">
-        <v>293.47868588</v>
+        <v>292.44802882</v>
       </c>
       <c r="P4">
-        <v>1173.91474352</v>
+        <v>1169.79211528</v>
       </c>
       <c r="Q4">
-        <v>1427.51474352</v>
+        <v>1423.39211528</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1170147129403599</v>
+        <v>0.1176044095655441</v>
       </c>
       <c r="T4">
-        <v>1.101668960194628</v>
+        <v>1.110791379440226</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>143.3745575856241</v>
+        <v>95.58303839041605</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1152834772785778</v>
+        <v>0.1150877358756028</v>
       </c>
       <c r="C5">
-        <v>9984.451852882747</v>
+        <v>9903.061816427626</v>
       </c>
       <c r="D5">
-        <v>9796.304852882746</v>
+        <v>9817.365816427626</v>
       </c>
       <c r="E5">
-        <v>37.95300000000003</v>
+        <v>140.4040000000001</v>
       </c>
       <c r="F5">
-        <v>307.353</v>
+        <v>409.804</v>
       </c>
       <c r="G5">
         <v>495.5</v>
@@ -1703,28 +1703,28 @@
         <v>1477.7</v>
       </c>
       <c r="M5">
-        <v>15.4598559</v>
+        <v>20.6131412</v>
       </c>
       <c r="N5">
-        <v>1462.2401441</v>
+        <v>1457.0868588</v>
       </c>
       <c r="O5">
-        <v>292.44802882</v>
+        <v>291.41737176</v>
       </c>
       <c r="P5">
-        <v>1169.79211528</v>
+        <v>1165.66948704</v>
       </c>
       <c r="Q5">
-        <v>1423.39211528</v>
+        <v>1419.26948704</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1176044095655441</v>
+        <v>0.1182063915370862</v>
       </c>
       <c r="T5">
-        <v>1.110791379440226</v>
+        <v>1.120103849086774</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>95.58303839041605</v>
+        <v>71.68727879281204</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1150877358756028</v>
+        <v>0.1148919944726277</v>
       </c>
       <c r="C6">
-        <v>9903.061816427626</v>
+        <v>9821.762532528755</v>
       </c>
       <c r="D6">
-        <v>9817.365816427626</v>
+        <v>9838.517532528755</v>
       </c>
       <c r="E6">
-        <v>140.4040000000001</v>
+        <v>242.855</v>
       </c>
       <c r="F6">
-        <v>409.804</v>
+        <v>512.255</v>
       </c>
       <c r="G6">
         <v>495.5</v>
@@ -1785,28 +1785,28 @@
         <v>1477.7</v>
       </c>
       <c r="M6">
-        <v>20.6131412</v>
+        <v>25.7664265</v>
       </c>
       <c r="N6">
-        <v>1457.0868588</v>
+        <v>1451.9335735</v>
       </c>
       <c r="O6">
-        <v>291.41737176</v>
+        <v>290.3867147</v>
       </c>
       <c r="P6">
-        <v>1165.66948704</v>
+        <v>1161.5468588</v>
       </c>
       <c r="Q6">
-        <v>1419.26948704</v>
+        <v>1415.1468588</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1182063915370862</v>
+        <v>0.1188210468132924</v>
       </c>
       <c r="T6">
-        <v>1.120103849086774</v>
+        <v>1.12961237072588</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>71.68727879281204</v>
+        <v>57.34982303424963</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1148919944726277</v>
+        <v>0.1146962530696528</v>
       </c>
       <c r="C7">
-        <v>9821.762532528755</v>
+        <v>9740.554589037392</v>
       </c>
       <c r="D7">
-        <v>9838.517532528755</v>
+        <v>9859.760589037392</v>
       </c>
       <c r="E7">
-        <v>242.855</v>
+        <v>345.306</v>
       </c>
       <c r="F7">
-        <v>512.255</v>
+        <v>614.706</v>
       </c>
       <c r="G7">
         <v>495.5</v>
@@ -1867,28 +1867,28 @@
         <v>1477.7</v>
       </c>
       <c r="M7">
-        <v>25.7664265</v>
+        <v>30.9197118</v>
       </c>
       <c r="N7">
-        <v>1451.9335735</v>
+        <v>1446.7802882</v>
       </c>
       <c r="O7">
-        <v>290.3867147</v>
+        <v>289.35605764</v>
       </c>
       <c r="P7">
-        <v>1161.5468588</v>
+        <v>1157.42423056</v>
       </c>
       <c r="Q7">
-        <v>1415.1468588</v>
+        <v>1411.02423056</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1188210468132924</v>
+        <v>0.1194487798613327</v>
       </c>
       <c r="T7">
-        <v>1.12961237072588</v>
+        <v>1.139323201336032</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.34982303424963</v>
+        <v>47.79151919520802</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1146962530696528</v>
+        <v>0.1145005116666778</v>
       </c>
       <c r="C8">
-        <v>9740.554589037392</v>
+        <v>9659.438578892899</v>
       </c>
       <c r="D8">
-        <v>9859.760589037392</v>
+        <v>9881.095578892899</v>
       </c>
       <c r="E8">
-        <v>345.306</v>
+        <v>447.7569999999999</v>
       </c>
       <c r="F8">
-        <v>614.706</v>
+        <v>717.1569999999999</v>
       </c>
       <c r="G8">
         <v>495.5</v>
@@ -1949,28 +1949,28 @@
         <v>1477.7</v>
       </c>
       <c r="M8">
-        <v>30.9197118</v>
+        <v>36.07299709999999</v>
       </c>
       <c r="N8">
-        <v>1446.7802882</v>
+        <v>1441.6270029</v>
       </c>
       <c r="O8">
-        <v>289.35605764</v>
+        <v>288.32540058</v>
       </c>
       <c r="P8">
-        <v>1157.42423056</v>
+        <v>1153.30160232</v>
       </c>
       <c r="Q8">
-        <v>1411.02423056</v>
+        <v>1406.90160232</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1194487798613327</v>
+        <v>0.1200900125448148</v>
       </c>
       <c r="T8">
-        <v>1.139323201336032</v>
+        <v>1.149242867013069</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.79151919520802</v>
+        <v>40.96415931017831</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1145005116666778</v>
+        <v>0.1143047702637027</v>
       </c>
       <c r="C9">
-        <v>9659.438578892901</v>
+        <v>9578.415100177863</v>
       </c>
       <c r="D9">
-        <v>9881.0955788929</v>
+        <v>9902.523100177863</v>
       </c>
       <c r="E9">
-        <v>447.7570000000001</v>
+        <v>550.2080000000001</v>
       </c>
       <c r="F9">
-        <v>717.157</v>
+        <v>819.6080000000001</v>
       </c>
       <c r="G9">
         <v>495.5</v>
@@ -2031,28 +2031,28 @@
         <v>1477.7</v>
       </c>
       <c r="M9">
-        <v>36.0729971</v>
+        <v>41.2262824</v>
       </c>
       <c r="N9">
-        <v>1441.6270029</v>
+        <v>1436.4737176</v>
       </c>
       <c r="O9">
-        <v>288.32540058</v>
+        <v>287.2947435200001</v>
       </c>
       <c r="P9">
-        <v>1153.30160232</v>
+        <v>1149.17897408</v>
       </c>
       <c r="Q9">
-        <v>1406.90160232</v>
+        <v>1402.77897408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1200900125448148</v>
+        <v>0.1207451850692421</v>
       </c>
       <c r="T9">
-        <v>1.149242867013069</v>
+        <v>1.159378177596128</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.9641593101783</v>
+        <v>35.84363939640602</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1143047702637027</v>
+        <v>0.1141090288607277</v>
       </c>
       <c r="C10">
-        <v>9578.415100177863</v>
+        <v>9497.484756173997</v>
       </c>
       <c r="D10">
-        <v>9902.523100177863</v>
+        <v>9924.043756173996</v>
       </c>
       <c r="E10">
-        <v>550.2080000000001</v>
+        <v>652.659</v>
       </c>
       <c r="F10">
-        <v>819.6080000000001</v>
+        <v>922.059</v>
       </c>
       <c r="G10">
         <v>495.5</v>
@@ -2113,28 +2113,28 @@
         <v>1477.7</v>
       </c>
       <c r="M10">
-        <v>41.2262824</v>
+        <v>46.3795677</v>
       </c>
       <c r="N10">
-        <v>1436.4737176</v>
+        <v>1431.3204323</v>
       </c>
       <c r="O10">
-        <v>287.2947435200001</v>
+        <v>286.26408646</v>
       </c>
       <c r="P10">
-        <v>1149.17897408</v>
+        <v>1145.05634584</v>
       </c>
       <c r="Q10">
-        <v>1402.77897408</v>
+        <v>1398.65634584</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1207451850692421</v>
+        <v>0.1214147569898107</v>
       </c>
       <c r="T10">
-        <v>1.159378177596128</v>
+        <v>1.169736242257935</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.84363939640602</v>
+        <v>31.86101279680535</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1141090288607277</v>
+        <v>0.1139132874577527</v>
       </c>
       <c r="C11">
-        <v>9497.484756173997</v>
+        <v>9416.648155418779</v>
       </c>
       <c r="D11">
-        <v>9924.043756173996</v>
+        <v>9945.65815541878</v>
       </c>
       <c r="E11">
-        <v>652.659</v>
+        <v>755.11</v>
       </c>
       <c r="F11">
-        <v>922.059</v>
+        <v>1024.51</v>
       </c>
       <c r="G11">
         <v>495.5</v>
@@ -2195,28 +2195,28 @@
         <v>1477.7</v>
       </c>
       <c r="M11">
-        <v>46.3795677</v>
+        <v>51.532853</v>
       </c>
       <c r="N11">
-        <v>1431.3204323</v>
+        <v>1426.167147</v>
       </c>
       <c r="O11">
-        <v>286.26408646</v>
+        <v>285.2334294</v>
       </c>
       <c r="P11">
-        <v>1145.05634584</v>
+        <v>1140.9337176</v>
       </c>
       <c r="Q11">
-        <v>1398.65634584</v>
+        <v>1394.5337176</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1214147569898107</v>
+        <v>0.1220992082863919</v>
       </c>
       <c r="T11">
-        <v>1.169736242257935</v>
+        <v>1.18032448613445</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.86101279680535</v>
+        <v>28.67491151712482</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1139132874577527</v>
+        <v>0.1137175460547777</v>
       </c>
       <c r="C12">
-        <v>9416.648155418779</v>
+        <v>9335.905911762795</v>
       </c>
       <c r="D12">
-        <v>9945.65815541878</v>
+        <v>9967.366911762794</v>
       </c>
       <c r="E12">
-        <v>755.11</v>
+        <v>857.561</v>
       </c>
       <c r="F12">
-        <v>1024.51</v>
+        <v>1126.961</v>
       </c>
       <c r="G12">
         <v>495.5</v>
@@ -2277,28 +2277,28 @@
         <v>1477.7</v>
       </c>
       <c r="M12">
-        <v>51.532853</v>
+        <v>56.6861383</v>
       </c>
       <c r="N12">
-        <v>1426.167147</v>
+        <v>1421.0138617</v>
       </c>
       <c r="O12">
-        <v>285.2334294</v>
+        <v>284.20277234</v>
       </c>
       <c r="P12">
-        <v>1140.9337176</v>
+        <v>1136.81108936</v>
       </c>
       <c r="Q12">
-        <v>1394.5337176</v>
+        <v>1390.41108936</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1220992082863919</v>
+        <v>0.1227990405109862</v>
       </c>
       <c r="T12">
-        <v>1.18032448613445</v>
+        <v>1.191150668075605</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.67491151712482</v>
+        <v>26.06810137920438</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1137175460547777</v>
+        <v>0.1135218046518027</v>
       </c>
       <c r="C13">
-        <v>9335.905911762795</v>
+        <v>9255.258644427833</v>
       </c>
       <c r="D13">
-        <v>9967.366911762794</v>
+        <v>9989.170644427833</v>
       </c>
       <c r="E13">
-        <v>857.561</v>
+        <v>960.0120000000001</v>
       </c>
       <c r="F13">
-        <v>1126.961</v>
+        <v>1229.412</v>
       </c>
       <c r="G13">
         <v>495.5</v>
@@ -2359,28 +2359,28 @@
         <v>1477.7</v>
       </c>
       <c r="M13">
-        <v>56.6861383</v>
+        <v>61.8394236</v>
       </c>
       <c r="N13">
-        <v>1421.0138617</v>
+        <v>1415.8605764</v>
       </c>
       <c r="O13">
-        <v>284.20277234</v>
+        <v>283.17211528</v>
       </c>
       <c r="P13">
-        <v>1136.81108936</v>
+        <v>1132.68846112</v>
       </c>
       <c r="Q13">
-        <v>1390.41108936</v>
+        <v>1386.28846112</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1227990405109862</v>
+        <v>0.1235147780134122</v>
       </c>
       <c r="T13">
-        <v>1.191150668075605</v>
+        <v>1.202222899606332</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.06810137920438</v>
+        <v>23.89575959760402</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1135218046518027</v>
+        <v>0.1133260632488277</v>
       </c>
       <c r="C14">
-        <v>9255.258644427833</v>
+        <v>9174.706978065806</v>
       </c>
       <c r="D14">
-        <v>9989.170644427833</v>
+        <v>10011.06997806581</v>
       </c>
       <c r="E14">
-        <v>960.0120000000001</v>
+        <v>1062.463</v>
       </c>
       <c r="F14">
-        <v>1229.412</v>
+        <v>1331.863</v>
       </c>
       <c r="G14">
         <v>495.5</v>
@@ -2441,28 +2441,28 @@
         <v>1477.7</v>
       </c>
       <c r="M14">
-        <v>61.8394236</v>
+        <v>66.9927089</v>
       </c>
       <c r="N14">
-        <v>1415.8605764</v>
+        <v>1410.7072911</v>
       </c>
       <c r="O14">
-        <v>283.17211528</v>
+        <v>282.14145822</v>
       </c>
       <c r="P14">
-        <v>1132.68846112</v>
+        <v>1128.56583288</v>
       </c>
       <c r="Q14">
-        <v>1386.28846112</v>
+        <v>1382.16583288</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1235147780134122</v>
+        <v>0.1242469692515261</v>
       </c>
       <c r="T14">
-        <v>1.202222899606332</v>
+        <v>1.213549665195236</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.89575959760402</v>
+        <v>22.05762424394216</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1133260632488277</v>
+        <v>0.1131303218458527</v>
       </c>
       <c r="C15">
-        <v>9174.706978065806</v>
+        <v>9094.251542818354</v>
       </c>
       <c r="D15">
-        <v>10011.06997806581</v>
+        <v>10033.06554281835</v>
       </c>
       <c r="E15">
-        <v>1062.463</v>
+        <v>1164.914</v>
       </c>
       <c r="F15">
-        <v>1331.863</v>
+        <v>1434.314</v>
       </c>
       <c r="G15">
         <v>495.5</v>
@@ -2523,28 +2523,28 @@
         <v>1477.7</v>
       </c>
       <c r="M15">
-        <v>66.9927089</v>
+        <v>72.1459942</v>
       </c>
       <c r="N15">
-        <v>1410.7072911</v>
+        <v>1405.5540058</v>
       </c>
       <c r="O15">
-        <v>282.14145822</v>
+        <v>281.1108011600001</v>
       </c>
       <c r="P15">
-        <v>1128.56583288</v>
+        <v>1124.44320464</v>
       </c>
       <c r="Q15">
-        <v>1382.16583288</v>
+        <v>1378.04320464</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1242469692515261</v>
+        <v>0.124996188192852</v>
       </c>
       <c r="T15">
-        <v>1.213549665195236</v>
+        <v>1.225139843937372</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.05762424394216</v>
+        <v>20.48207965508916</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1131303218458527</v>
+        <v>0.1129345804428777</v>
       </c>
       <c r="C16">
-        <v>9094.251542818354</v>
+        <v>9013.892974377333</v>
       </c>
       <c r="D16">
-        <v>10033.06554281835</v>
+        <v>10055.15797437733</v>
       </c>
       <c r="E16">
-        <v>1164.914</v>
+        <v>1267.365</v>
       </c>
       <c r="F16">
-        <v>1434.314</v>
+        <v>1536.765</v>
       </c>
       <c r="G16">
         <v>495.5</v>
@@ -2605,28 +2605,28 @@
         <v>1477.7</v>
       </c>
       <c r="M16">
-        <v>72.1459942</v>
+        <v>77.29927950000001</v>
       </c>
       <c r="N16">
-        <v>1405.5540058</v>
+        <v>1400.4007205</v>
       </c>
       <c r="O16">
-        <v>281.1108011600001</v>
+        <v>280.0801441</v>
       </c>
       <c r="P16">
-        <v>1124.44320464</v>
+        <v>1120.3205764</v>
       </c>
       <c r="Q16">
-        <v>1378.04320464</v>
+        <v>1373.9205764</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.124996188192852</v>
+        <v>0.1257630358151502</v>
       </c>
       <c r="T16">
-        <v>1.225139843937372</v>
+        <v>1.237002732767557</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.48207965508916</v>
+        <v>19.11660767808321</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1129345804428777</v>
+        <v>0.1127388390399027</v>
       </c>
       <c r="C17">
-        <v>9013.892974377335</v>
+        <v>8933.631914046016</v>
       </c>
       <c r="D17">
-        <v>10055.15797437733</v>
+        <v>10077.34791404602</v>
       </c>
       <c r="E17">
-        <v>1267.365</v>
+        <v>1369.816</v>
       </c>
       <c r="F17">
-        <v>1536.765</v>
+        <v>1639.216</v>
       </c>
       <c r="G17">
         <v>495.5</v>
@@ -2687,28 +2687,28 @@
         <v>1477.7</v>
       </c>
       <c r="M17">
-        <v>77.2992795</v>
+        <v>82.4525648</v>
       </c>
       <c r="N17">
-        <v>1400.4007205</v>
+        <v>1395.2474352</v>
       </c>
       <c r="O17">
-        <v>280.0801441</v>
+        <v>279.04948704</v>
       </c>
       <c r="P17">
-        <v>1120.3205764</v>
+        <v>1116.19794816</v>
       </c>
       <c r="Q17">
-        <v>1373.9205764</v>
+        <v>1369.79794816</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1257630358151502</v>
+        <v>0.1265481417141699</v>
       </c>
       <c r="T17">
-        <v>1.237002732767557</v>
+        <v>1.249148071331794</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.11660767808321</v>
+        <v>17.92181969820301</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1127388390399027</v>
+        <v>0.1125430976369277</v>
       </c>
       <c r="C18">
-        <v>8933.631914046016</v>
+        <v>8853.46900880117</v>
       </c>
       <c r="D18">
-        <v>10077.34791404602</v>
+        <v>10099.63600880117</v>
       </c>
       <c r="E18">
-        <v>1369.816</v>
+        <v>1472.267</v>
       </c>
       <c r="F18">
-        <v>1639.216</v>
+        <v>1741.667</v>
       </c>
       <c r="G18">
         <v>495.5</v>
@@ -2769,28 +2769,28 @@
         <v>1477.7</v>
       </c>
       <c r="M18">
-        <v>82.4525648</v>
+        <v>87.6058501</v>
       </c>
       <c r="N18">
-        <v>1395.2474352</v>
+        <v>1390.0941499</v>
       </c>
       <c r="O18">
-        <v>279.04948704</v>
+        <v>278.01882998</v>
       </c>
       <c r="P18">
-        <v>1116.19794816</v>
+        <v>1112.07531992</v>
       </c>
       <c r="Q18">
-        <v>1369.79794816</v>
+        <v>1365.67531992</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1265481417141699</v>
+        <v>0.1273521658276237</v>
       </c>
       <c r="T18">
-        <v>1.249148071331794</v>
+        <v>1.261586068656615</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.92181969820301</v>
+        <v>16.86759501007342</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1125430976369277</v>
+        <v>0.1123473562339527</v>
       </c>
       <c r="C19">
-        <v>8853.46900880117</v>
+        <v>8773.404911355923</v>
       </c>
       <c r="D19">
-        <v>10099.63600880117</v>
+        <v>10122.02291135592</v>
       </c>
       <c r="E19">
-        <v>1472.267</v>
+        <v>1574.718</v>
       </c>
       <c r="F19">
-        <v>1741.667</v>
+        <v>1844.118</v>
       </c>
       <c r="G19">
         <v>495.5</v>
@@ -2851,28 +2851,28 @@
         <v>1477.7</v>
       </c>
       <c r="M19">
-        <v>87.6058501</v>
+        <v>92.75913540000002</v>
       </c>
       <c r="N19">
-        <v>1390.0941499</v>
+        <v>1384.9408646</v>
       </c>
       <c r="O19">
-        <v>278.01882998</v>
+        <v>276.98817292</v>
       </c>
       <c r="P19">
-        <v>1112.07531992</v>
+        <v>1107.95269168</v>
       </c>
       <c r="Q19">
-        <v>1365.67531992</v>
+        <v>1361.55269168</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1273521658276237</v>
+        <v>0.1281758002853081</v>
       </c>
       <c r="T19">
-        <v>1.261586068656615</v>
+        <v>1.274327431769847</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.86759501007342</v>
+        <v>15.93050639840267</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1123473562339527</v>
+        <v>0.1121516148309777</v>
       </c>
       <c r="C20">
-        <v>8773.404911355921</v>
+        <v>8693.4402802235</v>
       </c>
       <c r="D20">
-        <v>10122.02291135592</v>
+        <v>10144.5092802235</v>
       </c>
       <c r="E20">
-        <v>1574.718</v>
+        <v>1677.169</v>
       </c>
       <c r="F20">
-        <v>1844.118</v>
+        <v>1946.569</v>
       </c>
       <c r="G20">
         <v>495.5</v>
@@ -2933,28 +2933,28 @@
         <v>1477.7</v>
       </c>
       <c r="M20">
-        <v>92.75913539999999</v>
+        <v>97.9124207</v>
       </c>
       <c r="N20">
-        <v>1384.9408646</v>
+        <v>1379.7875793</v>
       </c>
       <c r="O20">
-        <v>276.9881729200001</v>
+        <v>275.95751586</v>
       </c>
       <c r="P20">
-        <v>1107.95269168</v>
+        <v>1103.83006344</v>
       </c>
       <c r="Q20">
-        <v>1361.55269168</v>
+        <v>1357.43006344</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1281758002853081</v>
+        <v>0.1290197713962687</v>
       </c>
       <c r="T20">
-        <v>1.274327431769846</v>
+        <v>1.287383396441429</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.93050639840268</v>
+        <v>15.09205869322359</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1121516148309777</v>
+        <v>0.1119558734280027</v>
       </c>
       <c r="C21">
-        <v>8693.4402802235</v>
+        <v>8613.575779781773</v>
       </c>
       <c r="D21">
-        <v>10144.5092802235</v>
+        <v>10167.09577978177</v>
       </c>
       <c r="E21">
-        <v>1677.169</v>
+        <v>1779.62</v>
       </c>
       <c r="F21">
-        <v>1946.569</v>
+        <v>2049.02</v>
       </c>
       <c r="G21">
         <v>495.5</v>
@@ -3015,28 +3015,28 @@
         <v>1477.7</v>
       </c>
       <c r="M21">
-        <v>97.9124207</v>
+        <v>103.065706</v>
       </c>
       <c r="N21">
-        <v>1379.7875793</v>
+        <v>1374.634294</v>
       </c>
       <c r="O21">
-        <v>275.95751586</v>
+        <v>274.9268588</v>
       </c>
       <c r="P21">
-        <v>1103.83006344</v>
+        <v>1099.7074352</v>
       </c>
       <c r="Q21">
-        <v>1357.43006344</v>
+        <v>1353.3074352</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1290197713962687</v>
+        <v>0.1298848417850033</v>
       </c>
       <c r="T21">
-        <v>1.287383396441429</v>
+        <v>1.300765760229802</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.09205869322359</v>
+        <v>14.33745575856241</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1119558734280027</v>
+        <v>0.1117601320250277</v>
       </c>
       <c r="C22">
-        <v>8613.575779781773</v>
+        <v>8533.812080338703</v>
       </c>
       <c r="D22">
-        <v>10167.09577978177</v>
+        <v>10189.7830803387</v>
       </c>
       <c r="E22">
-        <v>1779.62</v>
+        <v>1882.071</v>
       </c>
       <c r="F22">
-        <v>2049.02</v>
+        <v>2151.471</v>
       </c>
       <c r="G22">
         <v>495.5</v>
@@ -3097,28 +3097,28 @@
         <v>1477.7</v>
       </c>
       <c r="M22">
-        <v>103.065706</v>
+        <v>108.2189913</v>
       </c>
       <c r="N22">
-        <v>1374.634294</v>
+        <v>1369.4810087</v>
       </c>
       <c r="O22">
-        <v>274.9268588</v>
+        <v>273.89620174</v>
       </c>
       <c r="P22">
-        <v>1099.7074352</v>
+        <v>1095.58480696</v>
       </c>
       <c r="Q22">
-        <v>1353.3074352</v>
+        <v>1349.18480696</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1298848417850033</v>
+        <v>0.1307718126899085</v>
       </c>
       <c r="T22">
-        <v>1.300765760229802</v>
+        <v>1.314486918038133</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.33745575856241</v>
+        <v>13.65471977005943</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1117601320250277</v>
+        <v>0.1115643906220527</v>
       </c>
       <c r="C23">
-        <v>8533.812080338703</v>
+        <v>8454.14985819864</v>
       </c>
       <c r="D23">
-        <v>10189.7830803387</v>
+        <v>10212.57185819864</v>
       </c>
       <c r="E23">
-        <v>1882.071</v>
+        <v>1984.522</v>
       </c>
       <c r="F23">
-        <v>2151.471</v>
+        <v>2253.922</v>
       </c>
       <c r="G23">
         <v>495.5</v>
@@ -3179,28 +3179,28 @@
         <v>1477.7</v>
       </c>
       <c r="M23">
-        <v>108.2189913</v>
+        <v>113.3722766</v>
       </c>
       <c r="N23">
-        <v>1369.4810087</v>
+        <v>1364.3277234</v>
       </c>
       <c r="O23">
-        <v>273.89620174</v>
+        <v>272.86554468</v>
       </c>
       <c r="P23">
-        <v>1095.58480696</v>
+        <v>1091.46217872</v>
       </c>
       <c r="Q23">
-        <v>1349.18480696</v>
+        <v>1345.06217872</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1307718126899085</v>
+        <v>0.1316815264385291</v>
       </c>
       <c r="T23">
-        <v>1.314486918038133</v>
+        <v>1.328559900405652</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.65471977005944</v>
+        <v>13.03405068960219</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1115643906220527</v>
+        <v>0.1113686492190777</v>
       </c>
       <c r="C24">
-        <v>8454.14985819864</v>
+        <v>8374.589795729551</v>
       </c>
       <c r="D24">
-        <v>10212.57185819864</v>
+        <v>10235.46279572955</v>
       </c>
       <c r="E24">
-        <v>1984.522</v>
+        <v>2086.973</v>
       </c>
       <c r="F24">
-        <v>2253.922</v>
+        <v>2356.373</v>
       </c>
       <c r="G24">
         <v>495.5</v>
@@ -3261,28 +3261,28 @@
         <v>1477.7</v>
       </c>
       <c r="M24">
-        <v>113.3722766</v>
+        <v>118.5255619</v>
       </c>
       <c r="N24">
-        <v>1364.3277234</v>
+        <v>1359.1744381</v>
       </c>
       <c r="O24">
-        <v>272.86554468</v>
+        <v>271.83488762</v>
       </c>
       <c r="P24">
-        <v>1091.46217872</v>
+        <v>1087.33955048</v>
       </c>
       <c r="Q24">
-        <v>1345.06217872</v>
+        <v>1340.93955048</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1316815264385291</v>
+        <v>0.1326148691156853</v>
       </c>
       <c r="T24">
-        <v>1.328559900405652</v>
+        <v>1.342998414782717</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.03405068960219</v>
+        <v>12.46735283353253</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1113686492190777</v>
+        <v>0.1111729078161027</v>
       </c>
       <c r="C25">
-        <v>8374.589795729551</v>
+        <v>8295.132581431099</v>
       </c>
       <c r="D25">
-        <v>10235.46279572955</v>
+        <v>10258.4565814311</v>
       </c>
       <c r="E25">
-        <v>2086.973</v>
+        <v>2189.424</v>
       </c>
       <c r="F25">
-        <v>2356.373</v>
+        <v>2458.824</v>
       </c>
       <c r="G25">
         <v>495.5</v>
@@ -3343,28 +3343,28 @@
         <v>1477.7</v>
       </c>
       <c r="M25">
-        <v>118.5255619</v>
+        <v>123.6788472</v>
       </c>
       <c r="N25">
-        <v>1359.1744381</v>
+        <v>1354.0211528</v>
       </c>
       <c r="O25">
-        <v>271.83488762</v>
+        <v>270.80423056</v>
       </c>
       <c r="P25">
-        <v>1087.33955048</v>
+        <v>1083.21692224</v>
       </c>
       <c r="Q25">
-        <v>1340.93955048</v>
+        <v>1336.81692224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1326148691156853</v>
+        <v>0.1335727734422403</v>
       </c>
       <c r="T25">
-        <v>1.342998414782717</v>
+        <v>1.357816890064442</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.46735283353253</v>
+        <v>11.94787979880201</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1111729078161026</v>
+        <v>0.1109771664131276</v>
       </c>
       <c r="C26">
-        <v>8295.132581431102</v>
+        <v>8215.778910003695</v>
       </c>
       <c r="D26">
-        <v>10258.4565814311</v>
+        <v>10281.55391000369</v>
       </c>
       <c r="E26">
-        <v>2189.424</v>
+        <v>2291.875</v>
       </c>
       <c r="F26">
-        <v>2458.824</v>
+        <v>2561.275</v>
       </c>
       <c r="G26">
         <v>495.5</v>
@@ -3425,28 +3425,28 @@
         <v>1477.7</v>
       </c>
       <c r="M26">
-        <v>123.6788472</v>
+        <v>128.8321325</v>
       </c>
       <c r="N26">
-        <v>1354.0211528</v>
+        <v>1348.8678675</v>
       </c>
       <c r="O26">
-        <v>270.80423056</v>
+        <v>269.7735735000001</v>
       </c>
       <c r="P26">
-        <v>1083.21692224</v>
+        <v>1079.094294</v>
       </c>
       <c r="Q26">
-        <v>1336.81692224</v>
+        <v>1332.694294</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1335727734422403</v>
+        <v>0.1345562218841702</v>
       </c>
       <c r="T26">
-        <v>1.357816890064442</v>
+        <v>1.373030524687013</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.94787979880201</v>
+        <v>11.46996460684993</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1109771664131276</v>
+        <v>0.1107814250101526</v>
       </c>
       <c r="C27">
-        <v>8215.778910003695</v>
+        <v>8136.529482418449</v>
       </c>
       <c r="D27">
-        <v>10281.55391000369</v>
+        <v>10304.75548241845</v>
       </c>
       <c r="E27">
-        <v>2291.875</v>
+        <v>2394.326</v>
       </c>
       <c r="F27">
-        <v>2561.275</v>
+        <v>2663.726</v>
       </c>
       <c r="G27">
         <v>495.5</v>
@@ -3507,28 +3507,28 @@
         <v>1477.7</v>
       </c>
       <c r="M27">
-        <v>128.8321325</v>
+        <v>133.9854178</v>
       </c>
       <c r="N27">
-        <v>1348.8678675</v>
+        <v>1343.7145822</v>
       </c>
       <c r="O27">
-        <v>269.7735735000001</v>
+        <v>268.74291644</v>
       </c>
       <c r="P27">
-        <v>1079.094294</v>
+        <v>1074.97166576</v>
       </c>
       <c r="Q27">
-        <v>1332.694294</v>
+        <v>1328.57166576</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1345562218841702</v>
+        <v>0.1355662500137198</v>
       </c>
       <c r="T27">
-        <v>1.373030524687013</v>
+        <v>1.388655338623707</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.46996460684993</v>
+        <v>11.02881212197108</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1107814250101526</v>
+        <v>0.1105856836071776</v>
       </c>
       <c r="C28">
-        <v>8136.529482418449</v>
+        <v>8057.385005988088</v>
       </c>
       <c r="D28">
-        <v>10304.75548241845</v>
+        <v>10328.06200598809</v>
       </c>
       <c r="E28">
-        <v>2394.326</v>
+        <v>2496.777</v>
       </c>
       <c r="F28">
-        <v>2663.726</v>
+        <v>2766.177</v>
       </c>
       <c r="G28">
         <v>495.5</v>
@@ -3589,28 +3589,28 @@
         <v>1477.7</v>
       </c>
       <c r="M28">
-        <v>133.9854178</v>
+        <v>139.1387031</v>
       </c>
       <c r="N28">
-        <v>1343.7145822</v>
+        <v>1338.5612969</v>
       </c>
       <c r="O28">
-        <v>268.74291644</v>
+        <v>267.71225938</v>
       </c>
       <c r="P28">
-        <v>1074.97166576</v>
+        <v>1070.84903752</v>
       </c>
       <c r="Q28">
-        <v>1328.57166576</v>
+        <v>1324.44903752</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1355662500137198</v>
+        <v>0.1366039501468187</v>
       </c>
       <c r="T28">
-        <v>1.388655338623707</v>
+        <v>1.404708229654558</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.02881212197108</v>
+        <v>10.62033759893512</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1105856836071776</v>
+        <v>0.1103899422042026</v>
       </c>
       <c r="C29">
-        <v>8057.385005988088</v>
+        <v>7978.346194438825</v>
       </c>
       <c r="D29">
-        <v>10328.06200598809</v>
+        <v>10351.47419443883</v>
       </c>
       <c r="E29">
-        <v>2496.777</v>
+        <v>2599.228</v>
       </c>
       <c r="F29">
-        <v>2766.177</v>
+        <v>2868.628</v>
       </c>
       <c r="G29">
         <v>495.5</v>
@@ -3671,28 +3671,28 @@
         <v>1477.7</v>
       </c>
       <c r="M29">
-        <v>139.1387031</v>
+        <v>144.2919884</v>
       </c>
       <c r="N29">
-        <v>1338.5612969</v>
+        <v>1333.4080116</v>
       </c>
       <c r="O29">
-        <v>267.71225938</v>
+        <v>266.68160232</v>
       </c>
       <c r="P29">
-        <v>1070.84903752</v>
+        <v>1066.72640928</v>
       </c>
       <c r="Q29">
-        <v>1324.44903752</v>
+        <v>1320.32640928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1366039501468187</v>
+        <v>0.1376704752836148</v>
       </c>
       <c r="T29">
-        <v>1.404708229654558</v>
+        <v>1.421207034325154</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.62033759893512</v>
+        <v>10.24103982754458</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1103899422042026</v>
+        <v>0.1101942008012276</v>
       </c>
       <c r="C30">
-        <v>7978.346194438825</v>
+        <v>7899.413767983239</v>
       </c>
       <c r="D30">
-        <v>10351.47419443883</v>
+        <v>10374.99276798324</v>
       </c>
       <c r="E30">
-        <v>2599.228</v>
+        <v>2701.679000000001</v>
       </c>
       <c r="F30">
-        <v>2868.628</v>
+        <v>2971.079000000001</v>
       </c>
       <c r="G30">
         <v>495.5</v>
@@ -3753,28 +3753,28 @@
         <v>1477.7</v>
       </c>
       <c r="M30">
-        <v>144.2919884</v>
+        <v>149.4452737</v>
       </c>
       <c r="N30">
-        <v>1333.4080116</v>
+        <v>1328.2547263</v>
       </c>
       <c r="O30">
-        <v>266.68160232</v>
+        <v>265.65094526</v>
       </c>
       <c r="P30">
-        <v>1066.72640928</v>
+        <v>1062.60378104</v>
       </c>
       <c r="Q30">
-        <v>1320.32640928</v>
+        <v>1316.20378104</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1376704752836148</v>
+        <v>0.1387670433820107</v>
       </c>
       <c r="T30">
-        <v>1.421207034325154</v>
+        <v>1.438170594056894</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.24103982754458</v>
+        <v>9.887900523146486</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1101942008012276</v>
+        <v>0.1099984593982526</v>
       </c>
       <c r="C31">
-        <v>7899.41376798324</v>
+        <v>7820.588453394099</v>
       </c>
       <c r="D31">
-        <v>10374.99276798324</v>
+        <v>10398.6184533941</v>
       </c>
       <c r="E31">
-        <v>2701.679</v>
+        <v>2804.13</v>
       </c>
       <c r="F31">
-        <v>2971.079</v>
+        <v>3073.53</v>
       </c>
       <c r="G31">
         <v>495.5</v>
@@ -3835,28 +3835,28 @@
         <v>1477.7</v>
       </c>
       <c r="M31">
-        <v>149.4452737</v>
+        <v>154.598559</v>
       </c>
       <c r="N31">
-        <v>1328.2547263</v>
+        <v>1323.101441</v>
       </c>
       <c r="O31">
-        <v>265.65094526</v>
+        <v>264.6202882</v>
       </c>
       <c r="P31">
-        <v>1062.60378104</v>
+        <v>1058.4811528</v>
       </c>
       <c r="Q31">
-        <v>1316.20378104</v>
+        <v>1312.0811528</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1387670433820107</v>
+        <v>0.1398949419975037</v>
       </c>
       <c r="T31">
-        <v>1.438170594056894</v>
+        <v>1.455618826923826</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.88790052314649</v>
+        <v>9.558303839041605</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1099984593982526</v>
+        <v>0.1098027179952776</v>
       </c>
       <c r="C32">
-        <v>7820.588453394099</v>
+        <v>7741.870984079247</v>
       </c>
       <c r="D32">
-        <v>10398.6184533941</v>
+        <v>10422.35198407925</v>
       </c>
       <c r="E32">
-        <v>2804.13</v>
+        <v>2906.581</v>
       </c>
       <c r="F32">
-        <v>3073.53</v>
+        <v>3175.981</v>
       </c>
       <c r="G32">
         <v>495.5</v>
@@ -3917,28 +3917,28 @@
         <v>1477.7</v>
       </c>
       <c r="M32">
-        <v>154.598559</v>
+        <v>159.7518443</v>
       </c>
       <c r="N32">
-        <v>1323.101441</v>
+        <v>1317.9481557</v>
       </c>
       <c r="O32">
-        <v>264.6202882</v>
+        <v>263.58963114</v>
       </c>
       <c r="P32">
-        <v>1058.4811528</v>
+        <v>1054.35852456</v>
       </c>
       <c r="Q32">
-        <v>1312.0811528</v>
+        <v>1307.95852456</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1398949419975037</v>
+        <v>0.1410555333264893</v>
       </c>
       <c r="T32">
-        <v>1.455618826923826</v>
+        <v>1.473572805670959</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.558303839041605</v>
+        <v>9.249971457137034</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1098027179952776</v>
+        <v>0.1096069765923026</v>
       </c>
       <c r="C33">
-        <v>7741.870984079247</v>
+        <v>7663.262100157481</v>
       </c>
       <c r="D33">
-        <v>10422.35198407925</v>
+        <v>10446.19410015748</v>
       </c>
       <c r="E33">
-        <v>2906.581</v>
+        <v>3009.032</v>
       </c>
       <c r="F33">
-        <v>3175.981</v>
+        <v>3278.432</v>
       </c>
       <c r="G33">
         <v>495.5</v>
@@ -3999,28 +3999,28 @@
         <v>1477.7</v>
       </c>
       <c r="M33">
-        <v>159.7518443</v>
+        <v>164.9051296</v>
       </c>
       <c r="N33">
-        <v>1317.9481557</v>
+        <v>1312.7948704</v>
       </c>
       <c r="O33">
-        <v>263.58963114</v>
+        <v>262.55897408</v>
       </c>
       <c r="P33">
-        <v>1054.35852456</v>
+        <v>1050.23589632</v>
       </c>
       <c r="Q33">
-        <v>1307.95852456</v>
+        <v>1303.83589632</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1410555333264893</v>
+        <v>0.1422502596945626</v>
       </c>
       <c r="T33">
-        <v>1.473572805670959</v>
+        <v>1.492054842616537</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.249971457137034</v>
+        <v>8.960909849101505</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1096069765923026</v>
+        <v>0.1098072351893276</v>
       </c>
       <c r="C34">
-        <v>7663.262100157481</v>
+        <v>7536.420055781779</v>
       </c>
       <c r="D34">
-        <v>10446.19410015748</v>
+        <v>10421.80305578178</v>
       </c>
       <c r="E34">
-        <v>3009.032</v>
+        <v>3111.483</v>
       </c>
       <c r="F34">
-        <v>3278.432</v>
+        <v>3380.883</v>
       </c>
       <c r="G34">
         <v>495.5</v>
@@ -4081,45 +4081,45 @@
         <v>1477.7</v>
       </c>
       <c r="M34">
-        <v>164.9051296</v>
+        <v>175.1297394</v>
       </c>
       <c r="N34">
-        <v>1312.7948704</v>
+        <v>1302.5702606</v>
       </c>
       <c r="O34">
-        <v>262.55897408</v>
+        <v>260.51405212</v>
       </c>
       <c r="P34">
-        <v>1050.23589632</v>
+        <v>1042.05620848</v>
       </c>
       <c r="Q34">
-        <v>1303.83589632</v>
+        <v>1295.65620848</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1422502596945626</v>
+        <v>0.1434806495363098</v>
       </c>
       <c r="T34">
-        <v>1.492054842616537</v>
+        <v>1.511088582157506</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>8.960909849101505</v>
+        <v>8.437744526216088</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1098072351893276</v>
+        <v>0.1096234937863526</v>
       </c>
       <c r="C35">
-        <v>7536.420055781779</v>
+        <v>7456.344024146072</v>
       </c>
       <c r="D35">
-        <v>10421.80305578178</v>
+        <v>10444.17802414607</v>
       </c>
       <c r="E35">
-        <v>3111.483</v>
+        <v>3213.934</v>
       </c>
       <c r="F35">
-        <v>3380.883</v>
+        <v>3483.334</v>
       </c>
       <c r="G35">
         <v>495.5</v>
@@ -4163,28 +4163,28 @@
         <v>1477.7</v>
       </c>
       <c r="M35">
-        <v>175.1297394</v>
+        <v>180.4367012</v>
       </c>
       <c r="N35">
-        <v>1302.5702606</v>
+        <v>1297.2632988</v>
       </c>
       <c r="O35">
-        <v>260.51405212</v>
+        <v>259.45265976</v>
       </c>
       <c r="P35">
-        <v>1042.05620848</v>
+        <v>1037.81063904</v>
       </c>
       <c r="Q35">
-        <v>1295.65620848</v>
+        <v>1291.41063904</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1434806495363098</v>
+        <v>0.1447483239187161</v>
       </c>
       <c r="T35">
-        <v>1.511088582157506</v>
+        <v>1.530699101684565</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.437744526216088</v>
+        <v>8.189575569562674</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1096234937863526</v>
+        <v>0.1094397523833776</v>
       </c>
       <c r="C36">
-        <v>7456.344024146072</v>
+        <v>7376.364274576092</v>
       </c>
       <c r="D36">
-        <v>10444.17802414607</v>
+        <v>10466.64927457609</v>
       </c>
       <c r="E36">
-        <v>3213.934</v>
+        <v>3316.385</v>
       </c>
       <c r="F36">
-        <v>3483.334</v>
+        <v>3585.785</v>
       </c>
       <c r="G36">
         <v>495.5</v>
@@ -4245,28 +4245,28 @@
         <v>1477.7</v>
       </c>
       <c r="M36">
-        <v>180.4367012</v>
+        <v>185.743663</v>
       </c>
       <c r="N36">
-        <v>1297.2632988</v>
+        <v>1291.956337</v>
       </c>
       <c r="O36">
-        <v>259.45265976</v>
+        <v>258.3912674</v>
       </c>
       <c r="P36">
-        <v>1037.81063904</v>
+        <v>1033.5650696</v>
       </c>
       <c r="Q36">
-        <v>1291.41063904</v>
+        <v>1287.1650696</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1447483239187161</v>
+        <v>0.1460550036667348</v>
       </c>
       <c r="T36">
-        <v>1.530699101684565</v>
+        <v>1.550913021812456</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.189575569562674</v>
+        <v>7.955587696146598</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1094397523833776</v>
+        <v>0.1092560109804026</v>
       </c>
       <c r="C37">
-        <v>7376.364274576092</v>
+        <v>7296.481429881071</v>
       </c>
       <c r="D37">
-        <v>10466.64927457609</v>
+        <v>10489.21742988107</v>
       </c>
       <c r="E37">
-        <v>3316.385</v>
+        <v>3418.836000000001</v>
       </c>
       <c r="F37">
-        <v>3585.785</v>
+        <v>3688.236000000001</v>
       </c>
       <c r="G37">
         <v>495.5</v>
@@ -4327,28 +4327,28 @@
         <v>1477.7</v>
       </c>
       <c r="M37">
-        <v>185.743663</v>
+        <v>191.0506248</v>
       </c>
       <c r="N37">
-        <v>1291.956337</v>
+        <v>1286.6493752</v>
       </c>
       <c r="O37">
-        <v>258.3912674</v>
+        <v>257.32987504</v>
       </c>
       <c r="P37">
-        <v>1033.5650696</v>
+        <v>1029.31950016</v>
       </c>
       <c r="Q37">
-        <v>1287.1650696</v>
+        <v>1282.91950016</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1460550036667348</v>
+        <v>0.147402517156879</v>
       </c>
       <c r="T37">
-        <v>1.550913021812456</v>
+        <v>1.571758626944344</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.955587696146598</v>
+        <v>7.734599149031413</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1092560109804026</v>
+        <v>0.1090722695774276</v>
       </c>
       <c r="C38">
-        <v>7296.481429881072</v>
+        <v>7216.696118253451</v>
       </c>
       <c r="D38">
-        <v>10489.21742988107</v>
+        <v>10511.88311825345</v>
       </c>
       <c r="E38">
-        <v>3418.836</v>
+        <v>3521.287</v>
       </c>
       <c r="F38">
-        <v>3688.236</v>
+        <v>3790.687</v>
       </c>
       <c r="G38">
         <v>495.5</v>
@@ -4409,28 +4409,28 @@
         <v>1477.7</v>
       </c>
       <c r="M38">
-        <v>191.0506248</v>
+        <v>196.3575866</v>
       </c>
       <c r="N38">
-        <v>1286.6493752</v>
+        <v>1281.3424134</v>
       </c>
       <c r="O38">
-        <v>257.32987504</v>
+        <v>256.26848268</v>
       </c>
       <c r="P38">
-        <v>1029.31950016</v>
+        <v>1025.07393072</v>
       </c>
       <c r="Q38">
-        <v>1282.91950016</v>
+        <v>1278.67393072</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.147402517156879</v>
+        <v>0.1487928088530596</v>
       </c>
       <c r="T38">
-        <v>1.571758626944344</v>
+        <v>1.593265997318514</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.734599149031416</v>
+        <v>7.525555928787323</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1090722695774276</v>
+        <v>0.1088885281744526</v>
       </c>
       <c r="C39">
-        <v>7216.696118253451</v>
+        <v>7137.008973327163</v>
       </c>
       <c r="D39">
-        <v>10511.88311825345</v>
+        <v>10534.64697332716</v>
       </c>
       <c r="E39">
-        <v>3521.287</v>
+        <v>3623.738</v>
       </c>
       <c r="F39">
-        <v>3790.687</v>
+        <v>3893.138</v>
       </c>
       <c r="G39">
         <v>495.5</v>
@@ -4491,28 +4491,28 @@
         <v>1477.7</v>
       </c>
       <c r="M39">
-        <v>196.3575866</v>
+        <v>201.6645484</v>
       </c>
       <c r="N39">
-        <v>1281.3424134</v>
+        <v>1276.0354516</v>
       </c>
       <c r="O39">
-        <v>256.26848268</v>
+        <v>255.20709032</v>
       </c>
       <c r="P39">
-        <v>1025.07393072</v>
+        <v>1020.82836128</v>
       </c>
       <c r="Q39">
-        <v>1278.67393072</v>
+        <v>1274.42836128</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1487928088530596</v>
+        <v>0.1502279486684719</v>
       </c>
       <c r="T39">
-        <v>1.593265997318514</v>
+        <v>1.615467153833786</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.525555928787323</v>
+        <v>7.327514983292919</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1088885281744526</v>
+        <v>0.1087047867714776</v>
       </c>
       <c r="C40">
-        <v>7137.008973327163</v>
+        <v>7057.420634236682</v>
       </c>
       <c r="D40">
-        <v>10534.64697332716</v>
+        <v>10557.50963423668</v>
       </c>
       <c r="E40">
-        <v>3623.738</v>
+        <v>3726.189</v>
       </c>
       <c r="F40">
-        <v>3893.138</v>
+        <v>3995.589</v>
       </c>
       <c r="G40">
         <v>495.5</v>
@@ -4573,28 +4573,28 @@
         <v>1477.7</v>
       </c>
       <c r="M40">
-        <v>201.6645484</v>
+        <v>206.9715102</v>
       </c>
       <c r="N40">
-        <v>1276.0354516</v>
+        <v>1270.7284898</v>
       </c>
       <c r="O40">
-        <v>255.20709032</v>
+        <v>254.14569796</v>
       </c>
       <c r="P40">
-        <v>1020.82836128</v>
+        <v>1016.58279184</v>
       </c>
       <c r="Q40">
-        <v>1274.42836128</v>
+        <v>1270.18279184</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1502279486684719</v>
+        <v>0.1517101422483239</v>
       </c>
       <c r="T40">
-        <v>1.615467153833786</v>
+        <v>1.638396217120051</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.327514983292919</v>
+        <v>7.139629983721306</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1087047867714776</v>
+        <v>0.1085210453685026</v>
       </c>
       <c r="C41">
-        <v>7057.420634236682</v>
+        <v>6977.931745676825</v>
       </c>
       <c r="D41">
-        <v>10557.50963423668</v>
+        <v>10580.47174567682</v>
       </c>
       <c r="E41">
-        <v>3726.189</v>
+        <v>3828.64</v>
       </c>
       <c r="F41">
-        <v>3995.589</v>
+        <v>4098.04</v>
       </c>
       <c r="G41">
         <v>495.5</v>
@@ -4655,28 +4655,28 @@
         <v>1477.7</v>
       </c>
       <c r="M41">
-        <v>206.9715102</v>
+        <v>212.278472</v>
       </c>
       <c r="N41">
-        <v>1270.7284898</v>
+        <v>1265.421528</v>
       </c>
       <c r="O41">
-        <v>254.14569796</v>
+        <v>253.0843056</v>
       </c>
       <c r="P41">
-        <v>1016.58279184</v>
+        <v>1012.3372224</v>
       </c>
       <c r="Q41">
-        <v>1270.18279184</v>
+        <v>1265.9372224</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1517101422483239</v>
+        <v>0.1532417422808376</v>
       </c>
       <c r="T41">
-        <v>1.638396217120051</v>
+        <v>1.662089582515858</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.139629983721306</v>
+        <v>6.961139234128273</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1085210453685026</v>
+        <v>0.1083373039655276</v>
       </c>
       <c r="C42">
-        <v>6977.931745676825</v>
+        <v>6898.542957963379</v>
       </c>
       <c r="D42">
-        <v>10580.47174567682</v>
+        <v>10603.53395796338</v>
       </c>
       <c r="E42">
-        <v>3828.64</v>
+        <v>3931.091000000001</v>
       </c>
       <c r="F42">
-        <v>4098.04</v>
+        <v>4200.491000000001</v>
       </c>
       <c r="G42">
         <v>495.5</v>
@@ -4737,28 +4737,28 @@
         <v>1477.7</v>
       </c>
       <c r="M42">
-        <v>212.278472</v>
+        <v>217.5854338</v>
       </c>
       <c r="N42">
-        <v>1265.421528</v>
+        <v>1260.1145662</v>
       </c>
       <c r="O42">
-        <v>253.0843056</v>
+        <v>252.02291324</v>
       </c>
       <c r="P42">
-        <v>1012.3372224</v>
+        <v>1008.09165296</v>
       </c>
       <c r="Q42">
-        <v>1265.9372224</v>
+        <v>1261.69165296</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1532417422808376</v>
+        <v>0.1548252609585213</v>
       </c>
       <c r="T42">
-        <v>1.662089582515858</v>
+        <v>1.686586112840336</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.961139234128273</v>
+        <v>6.791355350369045</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1083373039655276</v>
+        <v>0.1087247625625526</v>
       </c>
       <c r="C43">
-        <v>6898.542957963379</v>
+        <v>6747.5772705326</v>
       </c>
       <c r="D43">
-        <v>10603.53395796338</v>
+        <v>10555.0192705326</v>
       </c>
       <c r="E43">
-        <v>3931.091000000001</v>
+        <v>4033.542000000001</v>
       </c>
       <c r="F43">
-        <v>4200.491000000001</v>
+        <v>4302.942000000001</v>
       </c>
       <c r="G43">
         <v>495.5</v>
@@ -4819,45 +4819,45 @@
         <v>1477.7</v>
       </c>
       <c r="M43">
-        <v>217.5854338</v>
+        <v>230.207397</v>
       </c>
       <c r="N43">
-        <v>1260.1145662</v>
+        <v>1247.492603</v>
       </c>
       <c r="O43">
-        <v>252.02291324</v>
+        <v>249.4985206</v>
       </c>
       <c r="P43">
-        <v>1008.09165296</v>
+        <v>997.9940823999999</v>
       </c>
       <c r="Q43">
-        <v>1261.69165296</v>
+        <v>1251.5940824</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1548252609585213</v>
+        <v>0.1564633837285389</v>
       </c>
       <c r="T43">
-        <v>1.686586112840336</v>
+        <v>1.711927351107038</v>
       </c>
       <c r="U43">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.791355350369045</v>
+        <v>6.418994433962518</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1087247625625526</v>
+        <v>0.1085546211595776</v>
       </c>
       <c r="C44">
-        <v>6747.577270532601</v>
+        <v>6666.375333088947</v>
       </c>
       <c r="D44">
-        <v>10555.0192705326</v>
+        <v>10576.26833308895</v>
       </c>
       <c r="E44">
-        <v>4033.542</v>
+        <v>4135.993</v>
       </c>
       <c r="F44">
-        <v>4302.942</v>
+        <v>4405.393</v>
       </c>
       <c r="G44">
         <v>495.5</v>
@@ -4901,28 +4901,28 @@
         <v>1477.7</v>
       </c>
       <c r="M44">
-        <v>230.207397</v>
+        <v>235.6885255</v>
       </c>
       <c r="N44">
-        <v>1247.492603</v>
+        <v>1242.0114745</v>
       </c>
       <c r="O44">
-        <v>249.4985206</v>
+        <v>248.4022949</v>
       </c>
       <c r="P44">
-        <v>997.9940824000001</v>
+        <v>993.6091796000001</v>
       </c>
       <c r="Q44">
-        <v>1251.5940824</v>
+        <v>1247.2091796</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1564633837285389</v>
+        <v>0.1581589844904869</v>
       </c>
       <c r="T44">
-        <v>1.711927351107038</v>
+        <v>1.738157755628712</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.418994433962521</v>
+        <v>6.26971549363781</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1085546211595776</v>
+        <v>0.1083844797566026</v>
       </c>
       <c r="C45">
-        <v>6666.375333088947</v>
+        <v>6585.259124240204</v>
       </c>
       <c r="D45">
-        <v>10576.26833308895</v>
+        <v>10597.6031242402</v>
       </c>
       <c r="E45">
-        <v>4135.993</v>
+        <v>4238.444</v>
       </c>
       <c r="F45">
-        <v>4405.393</v>
+        <v>4507.844</v>
       </c>
       <c r="G45">
         <v>495.5</v>
@@ -4983,28 +4983,28 @@
         <v>1477.7</v>
       </c>
       <c r="M45">
-        <v>235.6885255</v>
+        <v>241.169654</v>
       </c>
       <c r="N45">
-        <v>1242.0114745</v>
+        <v>1236.530346</v>
       </c>
       <c r="O45">
-        <v>248.4022949</v>
+        <v>247.3060692</v>
       </c>
       <c r="P45">
-        <v>993.6091796000001</v>
+        <v>989.2242768</v>
       </c>
       <c r="Q45">
-        <v>1247.2091796</v>
+        <v>1242.8242768</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1581589844904869</v>
+        <v>0.1599151424225045</v>
       </c>
       <c r="T45">
-        <v>1.738157755628712</v>
+        <v>1.765324960311874</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.26971549363781</v>
+        <v>6.127221959691496</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1083844797566026</v>
+        <v>0.1082143383536275</v>
       </c>
       <c r="C46">
-        <v>6585.259124240204</v>
+        <v>6504.229163838536</v>
       </c>
       <c r="D46">
-        <v>10597.6031242402</v>
+        <v>10619.02416383854</v>
       </c>
       <c r="E46">
-        <v>4238.444</v>
+        <v>4340.895</v>
       </c>
       <c r="F46">
-        <v>4507.844</v>
+        <v>4610.295</v>
       </c>
       <c r="G46">
         <v>495.5</v>
@@ -5065,28 +5065,28 @@
         <v>1477.7</v>
       </c>
       <c r="M46">
-        <v>241.169654</v>
+        <v>246.6507825</v>
       </c>
       <c r="N46">
-        <v>1236.530346</v>
+        <v>1231.0492175</v>
       </c>
       <c r="O46">
-        <v>247.3060692</v>
+        <v>246.2098435</v>
       </c>
       <c r="P46">
-        <v>989.2242768</v>
+        <v>984.8393739999999</v>
       </c>
       <c r="Q46">
-        <v>1242.8242768</v>
+        <v>1238.439374</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1599151424225045</v>
+        <v>0.1617351606429591</v>
       </c>
       <c r="T46">
-        <v>1.765324960311874</v>
+        <v>1.793480063347151</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.127221959691496</v>
+        <v>5.991061471698352</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1082143383536275</v>
+        <v>0.1080441969506525</v>
       </c>
       <c r="C47">
-        <v>6504.229163838536</v>
+        <v>6423.285975947739</v>
       </c>
       <c r="D47">
-        <v>10619.02416383854</v>
+        <v>10640.53197594774</v>
       </c>
       <c r="E47">
-        <v>4340.895</v>
+        <v>4443.346</v>
       </c>
       <c r="F47">
-        <v>4610.295</v>
+        <v>4712.746</v>
       </c>
       <c r="G47">
         <v>495.5</v>
@@ -5147,28 +5147,28 @@
         <v>1477.7</v>
       </c>
       <c r="M47">
-        <v>246.6507825</v>
+        <v>252.131911</v>
       </c>
       <c r="N47">
-        <v>1231.0492175</v>
+        <v>1225.568089</v>
       </c>
       <c r="O47">
-        <v>246.2098435</v>
+        <v>245.1136178</v>
       </c>
       <c r="P47">
-        <v>984.8393739999999</v>
+        <v>980.4544712000001</v>
       </c>
       <c r="Q47">
-        <v>1238.439374</v>
+        <v>1234.0544712</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1617351606429591</v>
+        <v>0.1636225869456528</v>
       </c>
       <c r="T47">
-        <v>1.793480063347151</v>
+        <v>1.822677947976327</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.991061471698352</v>
+        <v>5.8608210049223</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1080441969506525</v>
+        <v>0.1078740555476775</v>
       </c>
       <c r="C48">
-        <v>6423.285975947739</v>
+        <v>6342.430088886</v>
       </c>
       <c r="D48">
-        <v>10640.53197594774</v>
+        <v>10662.127088886</v>
       </c>
       <c r="E48">
-        <v>4443.346</v>
+        <v>4545.797</v>
       </c>
       <c r="F48">
-        <v>4712.746</v>
+        <v>4815.197</v>
       </c>
       <c r="G48">
         <v>495.5</v>
@@ -5229,28 +5229,28 @@
         <v>1477.7</v>
       </c>
       <c r="M48">
-        <v>252.131911</v>
+        <v>257.6130395</v>
       </c>
       <c r="N48">
-        <v>1225.568089</v>
+        <v>1220.0869605</v>
       </c>
       <c r="O48">
-        <v>245.1136178</v>
+        <v>244.0173921</v>
       </c>
       <c r="P48">
-        <v>980.4544712000001</v>
+        <v>976.0695684</v>
       </c>
       <c r="Q48">
-        <v>1234.0544712</v>
+        <v>1229.6695684</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1636225869456528</v>
+        <v>0.1655812368824104</v>
       </c>
       <c r="T48">
-        <v>1.822677947976327</v>
+        <v>1.852977639572642</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.8608210049223</v>
+        <v>5.736122685668635</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1078740555476775</v>
+        <v>0.1077039141447025</v>
       </c>
       <c r="C49">
-        <v>6342.430088886</v>
+        <v>6261.662035269138</v>
       </c>
       <c r="D49">
-        <v>10662.127088886</v>
+        <v>10683.81003526914</v>
       </c>
       <c r="E49">
-        <v>4545.797</v>
+        <v>4648.248000000001</v>
       </c>
       <c r="F49">
-        <v>4815.197</v>
+        <v>4917.648</v>
       </c>
       <c r="G49">
         <v>495.5</v>
@@ -5311,28 +5311,28 @@
         <v>1477.7</v>
       </c>
       <c r="M49">
-        <v>257.6130395</v>
+        <v>263.094168</v>
       </c>
       <c r="N49">
-        <v>1220.0869605</v>
+        <v>1214.605832</v>
       </c>
       <c r="O49">
-        <v>244.0173921</v>
+        <v>242.9211664</v>
       </c>
       <c r="P49">
-        <v>976.0695684</v>
+        <v>971.6846656</v>
       </c>
       <c r="Q49">
-        <v>1229.6695684</v>
+        <v>1225.2846656</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1655812368824104</v>
+        <v>0.1676152195090433</v>
       </c>
       <c r="T49">
-        <v>1.852977639572642</v>
+        <v>1.884442703922662</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.736122685668635</v>
+        <v>5.616620129717204</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1077039141447025</v>
+        <v>0.1078473727417275</v>
       </c>
       <c r="C50">
-        <v>6261.662035269138</v>
+        <v>6140.922744580132</v>
       </c>
       <c r="D50">
-        <v>10683.81003526914</v>
+        <v>10665.52174458013</v>
       </c>
       <c r="E50">
-        <v>4648.248000000001</v>
+        <v>4750.699000000001</v>
       </c>
       <c r="F50">
-        <v>4917.648</v>
+        <v>5020.099</v>
       </c>
       <c r="G50">
         <v>495.5</v>
@@ -5393,45 +5393,45 @@
         <v>1477.7</v>
       </c>
       <c r="M50">
-        <v>263.094168</v>
+        <v>272.5913757</v>
       </c>
       <c r="N50">
-        <v>1214.605832</v>
+        <v>1205.1086243</v>
       </c>
       <c r="O50">
-        <v>242.9211664</v>
+        <v>241.02172486</v>
       </c>
       <c r="P50">
-        <v>971.6846656</v>
+        <v>964.08689944</v>
       </c>
       <c r="Q50">
-        <v>1225.2846656</v>
+        <v>1217.68689944</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1676152195090433</v>
+        <v>0.16972896616025</v>
       </c>
       <c r="T50">
-        <v>1.884442703922662</v>
+        <v>1.917141692364839</v>
       </c>
       <c r="U50">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y50">
-        <v>5.616620129717204</v>
+        <v>5.420934525919412</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1078473727417275</v>
+        <v>0.1076836313387525</v>
       </c>
       <c r="C51">
-        <v>6140.922744580132</v>
+        <v>6059.35077583128</v>
       </c>
       <c r="D51">
-        <v>10665.52174458013</v>
+        <v>10686.40077583128</v>
       </c>
       <c r="E51">
-        <v>4750.699000000001</v>
+        <v>4853.150000000001</v>
       </c>
       <c r="F51">
-        <v>5020.099</v>
+        <v>5122.55</v>
       </c>
       <c r="G51">
         <v>495.5</v>
@@ -5475,28 +5475,28 @@
         <v>1477.7</v>
       </c>
       <c r="M51">
-        <v>272.5913757</v>
+        <v>278.154465</v>
       </c>
       <c r="N51">
-        <v>1205.1086243</v>
+        <v>1199.545535</v>
       </c>
       <c r="O51">
-        <v>241.02172486</v>
+        <v>239.909107</v>
       </c>
       <c r="P51">
-        <v>964.08689944</v>
+        <v>959.636428</v>
       </c>
       <c r="Q51">
-        <v>1217.68689944</v>
+        <v>1213.236428</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.16972896616025</v>
+        <v>0.171927262677505</v>
       </c>
       <c r="T51">
-        <v>1.917141692364839</v>
+        <v>1.951148640344703</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.420934525919412</v>
+        <v>5.312515835401024</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1076836313387525</v>
+        <v>0.1075198899357775</v>
       </c>
       <c r="C52">
-        <v>6059.35077583128</v>
+        <v>5977.860713813869</v>
       </c>
       <c r="D52">
-        <v>10686.40077583128</v>
+        <v>10707.36171381387</v>
       </c>
       <c r="E52">
-        <v>4853.150000000001</v>
+        <v>4955.601000000001</v>
       </c>
       <c r="F52">
-        <v>5122.55</v>
+        <v>5225.001</v>
       </c>
       <c r="G52">
         <v>495.5</v>
@@ -5557,28 +5557,28 @@
         <v>1477.7</v>
       </c>
       <c r="M52">
-        <v>278.154465</v>
+        <v>283.7175543</v>
       </c>
       <c r="N52">
-        <v>1199.545535</v>
+        <v>1193.9824457</v>
       </c>
       <c r="O52">
-        <v>239.909107</v>
+        <v>238.79648914</v>
       </c>
       <c r="P52">
-        <v>959.636428</v>
+        <v>955.18595656</v>
       </c>
       <c r="Q52">
-        <v>1213.236428</v>
+        <v>1208.78595656</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.171927262677505</v>
+        <v>0.1742152855832194</v>
       </c>
       <c r="T52">
-        <v>1.951148640344703</v>
+        <v>1.986543627017623</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.312515835401024</v>
+        <v>5.208348858236298</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1075198899357775</v>
+        <v>0.1073561485328025</v>
       </c>
       <c r="C53">
-        <v>5977.860713813869</v>
+        <v>5896.453041445225</v>
       </c>
       <c r="D53">
-        <v>10707.36171381387</v>
+        <v>10728.40504144522</v>
       </c>
       <c r="E53">
-        <v>4955.601000000001</v>
+        <v>5058.052000000001</v>
       </c>
       <c r="F53">
-        <v>5225.001</v>
+        <v>5327.452</v>
       </c>
       <c r="G53">
         <v>495.5</v>
@@ -5639,28 +5639,28 @@
         <v>1477.7</v>
       </c>
       <c r="M53">
-        <v>283.7175543</v>
+        <v>289.2806436</v>
       </c>
       <c r="N53">
-        <v>1193.9824457</v>
+        <v>1188.4193564</v>
       </c>
       <c r="O53">
-        <v>238.79648914</v>
+        <v>237.68387128</v>
       </c>
       <c r="P53">
-        <v>955.18595656</v>
+        <v>950.73548512</v>
       </c>
       <c r="Q53">
-        <v>1208.78595656</v>
+        <v>1204.33548512</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1742152855832194</v>
+        <v>0.1765986427766719</v>
       </c>
       <c r="T53">
-        <v>1.986543627017623</v>
+        <v>2.023413404801914</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.208348858236298</v>
+        <v>5.108188303270215</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1073561485328025</v>
+        <v>0.1071924071298275</v>
       </c>
       <c r="C54">
-        <v>5896.453041445225</v>
+        <v>5815.1282454465</v>
       </c>
       <c r="D54">
-        <v>10728.40504144522</v>
+        <v>10749.5312454465</v>
       </c>
       <c r="E54">
-        <v>5058.052000000001</v>
+        <v>5160.503000000001</v>
       </c>
       <c r="F54">
-        <v>5327.452</v>
+        <v>5429.903</v>
       </c>
       <c r="G54">
         <v>495.5</v>
@@ -5721,28 +5721,28 @@
         <v>1477.7</v>
       </c>
       <c r="M54">
-        <v>289.2806436</v>
+        <v>294.8437329</v>
       </c>
       <c r="N54">
-        <v>1188.4193564</v>
+        <v>1182.8562671</v>
       </c>
       <c r="O54">
-        <v>237.68387128</v>
+        <v>236.57125342</v>
       </c>
       <c r="P54">
-        <v>950.73548512</v>
+        <v>946.28501368</v>
       </c>
       <c r="Q54">
-        <v>1204.33548512</v>
+        <v>1199.88501368</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1765986427766719</v>
+        <v>0.1790834194251649</v>
       </c>
       <c r="T54">
-        <v>2.023413404801914</v>
+        <v>2.061852109300431</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.108188303270215</v>
+        <v>5.011807391887759</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1071924071298275</v>
+        <v>0.1070286657268525</v>
       </c>
       <c r="C55">
-        <v>5815.1282454465</v>
+        <v>5733.886816380168</v>
       </c>
       <c r="D55">
-        <v>10749.5312454465</v>
+        <v>10770.74081638017</v>
       </c>
       <c r="E55">
-        <v>5160.503000000001</v>
+        <v>5262.954000000001</v>
       </c>
       <c r="F55">
-        <v>5429.903</v>
+        <v>5532.354</v>
       </c>
       <c r="G55">
         <v>495.5</v>
@@ -5803,28 +5803,28 @@
         <v>1477.7</v>
       </c>
       <c r="M55">
-        <v>294.8437329</v>
+        <v>300.4068222</v>
       </c>
       <c r="N55">
-        <v>1182.8562671</v>
+        <v>1177.2931778</v>
       </c>
       <c r="O55">
-        <v>236.57125342</v>
+        <v>235.45863556</v>
       </c>
       <c r="P55">
-        <v>946.28501368</v>
+        <v>941.83454224</v>
       </c>
       <c r="Q55">
-        <v>1199.88501368</v>
+        <v>1195.43454224</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1790834194251649</v>
+        <v>0.1816762298409837</v>
       </c>
       <c r="T55">
-        <v>2.061852109300431</v>
+        <v>2.101962061820622</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.011807391887759</v>
+        <v>4.918996143889837</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1070286657268525</v>
+        <v>0.1068649243238775</v>
       </c>
       <c r="C56">
-        <v>5733.886816380168</v>
+        <v>5652.729248688029</v>
       </c>
       <c r="D56">
-        <v>10770.74081638017</v>
+        <v>10792.03424868803</v>
       </c>
       <c r="E56">
-        <v>5262.954000000001</v>
+        <v>5365.405000000001</v>
       </c>
       <c r="F56">
-        <v>5532.354</v>
+        <v>5634.805</v>
       </c>
       <c r="G56">
         <v>495.5</v>
@@ -5885,28 +5885,28 @@
         <v>1477.7</v>
       </c>
       <c r="M56">
-        <v>300.4068222</v>
+        <v>305.9699115</v>
       </c>
       <c r="N56">
-        <v>1177.2931778</v>
+        <v>1171.7300885</v>
       </c>
       <c r="O56">
-        <v>235.45863556</v>
+        <v>234.3460177</v>
       </c>
       <c r="P56">
-        <v>941.83454224</v>
+        <v>937.3840708</v>
       </c>
       <c r="Q56">
-        <v>1195.43454224</v>
+        <v>1190.9840708</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1816762298409837</v>
+        <v>0.1843842762752833</v>
       </c>
       <c r="T56">
-        <v>2.101962061820622</v>
+        <v>2.143854678897266</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.918996143889837</v>
+        <v>4.829559850364568</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1068649243238775</v>
+        <v>0.1067011829209025</v>
       </c>
       <c r="C57">
-        <v>5652.729248688029</v>
+        <v>5571.656040729608</v>
       </c>
       <c r="D57">
-        <v>10792.03424868803</v>
+        <v>10813.41204072961</v>
       </c>
       <c r="E57">
-        <v>5365.405000000001</v>
+        <v>5467.856000000001</v>
       </c>
       <c r="F57">
-        <v>5634.805</v>
+        <v>5737.256</v>
       </c>
       <c r="G57">
         <v>495.5</v>
@@ -5967,28 +5967,28 @@
         <v>1477.7</v>
       </c>
       <c r="M57">
-        <v>305.9699115</v>
+        <v>311.5330008</v>
       </c>
       <c r="N57">
-        <v>1171.7300885</v>
+        <v>1166.1669992</v>
       </c>
       <c r="O57">
-        <v>234.3460177</v>
+        <v>233.23339984</v>
       </c>
       <c r="P57">
-        <v>937.3840708</v>
+        <v>932.93359936</v>
       </c>
       <c r="Q57">
-        <v>1190.9840708</v>
+        <v>1186.53359936</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1843842762752833</v>
+        <v>0.1872154157293238</v>
       </c>
       <c r="T57">
-        <v>2.143854678897266</v>
+        <v>2.187651505841031</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.829559850364568</v>
+        <v>4.743317710179486</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1067011829209025</v>
+        <v>0.1065374415179275</v>
       </c>
       <c r="C58">
-        <v>5571.656040729608</v>
+        <v>5490.667694821029</v>
       </c>
       <c r="D58">
-        <v>10813.41204072961</v>
+        <v>10834.87469482103</v>
       </c>
       <c r="E58">
-        <v>5467.856000000001</v>
+        <v>5570.307000000002</v>
       </c>
       <c r="F58">
-        <v>5737.256</v>
+        <v>5839.707000000001</v>
       </c>
       <c r="G58">
         <v>495.5</v>
@@ -6049,28 +6049,28 @@
         <v>1477.7</v>
       </c>
       <c r="M58">
-        <v>311.5330008</v>
+        <v>317.0960901000001</v>
       </c>
       <c r="N58">
-        <v>1166.1669992</v>
+        <v>1160.6039099</v>
       </c>
       <c r="O58">
-        <v>233.23339984</v>
+        <v>232.12078198</v>
       </c>
       <c r="P58">
-        <v>932.93359936</v>
+        <v>928.48312792</v>
       </c>
       <c r="Q58">
-        <v>1186.53359936</v>
+        <v>1182.08312792</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1872154157293238</v>
+        <v>0.1901782360882034</v>
       </c>
       <c r="T58">
-        <v>2.187651505841031</v>
+        <v>2.23348539450311</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.743317710179486</v>
+        <v>4.660101610000897</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1065374415179275</v>
+        <v>0.1063737001149525</v>
       </c>
       <c r="C59">
-        <v>5490.667694821029</v>
+        <v>5409.764717274396</v>
       </c>
       <c r="D59">
-        <v>10834.87469482103</v>
+        <v>10856.4227172744</v>
       </c>
       <c r="E59">
-        <v>5570.307000000002</v>
+        <v>5672.758000000002</v>
       </c>
       <c r="F59">
-        <v>5839.707000000001</v>
+        <v>5942.158000000001</v>
       </c>
       <c r="G59">
         <v>495.5</v>
@@ -6131,28 +6131,28 @@
         <v>1477.7</v>
       </c>
       <c r="M59">
-        <v>317.0960901000001</v>
+        <v>322.6591794000001</v>
       </c>
       <c r="N59">
-        <v>1160.6039099</v>
+        <v>1155.0408206</v>
       </c>
       <c r="O59">
-        <v>232.12078198</v>
+        <v>231.00816412</v>
       </c>
       <c r="P59">
-        <v>928.48312792</v>
+        <v>924.03265648</v>
       </c>
       <c r="Q59">
-        <v>1182.08312792</v>
+        <v>1177.63265648</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1901782360882034</v>
+        <v>0.1932821431308392</v>
       </c>
       <c r="T59">
-        <v>2.23348539450311</v>
+        <v>2.281501849291955</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.660101610000897</v>
+        <v>4.579755030518124</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1063737001149525</v>
+        <v>0.1062099587119775</v>
       </c>
       <c r="C60">
-        <v>5409.7647172744</v>
+        <v>5328.94761843757</v>
       </c>
       <c r="D60">
-        <v>10856.4227172744</v>
+        <v>10878.05661843757</v>
       </c>
       <c r="E60">
-        <v>5672.758</v>
+        <v>5775.209</v>
       </c>
       <c r="F60">
-        <v>5942.157999999999</v>
+        <v>6044.608999999999</v>
       </c>
       <c r="G60">
         <v>495.5</v>
@@ -6213,28 +6213,28 @@
         <v>1477.7</v>
       </c>
       <c r="M60">
-        <v>322.6591794</v>
+        <v>328.2222687</v>
       </c>
       <c r="N60">
-        <v>1155.0408206</v>
+        <v>1149.4777313</v>
       </c>
       <c r="O60">
-        <v>231.0081641200001</v>
+        <v>229.89554626</v>
       </c>
       <c r="P60">
-        <v>924.0326564800001</v>
+        <v>919.58218504</v>
       </c>
       <c r="Q60">
-        <v>1177.63265648</v>
+        <v>1173.18218504</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1932821431308392</v>
+        <v>0.1965374602731157</v>
       </c>
       <c r="T60">
-        <v>2.281501849291954</v>
+        <v>2.331860570168059</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.579755030518125</v>
+        <v>4.502132063899174</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1062099587119775</v>
+        <v>0.1060462173090025</v>
       </c>
       <c r="C61">
-        <v>5328.94761843757</v>
+        <v>5248.216912734467</v>
       </c>
       <c r="D61">
-        <v>10878.05661843757</v>
+        <v>10899.77691273447</v>
       </c>
       <c r="E61">
-        <v>5775.209</v>
+        <v>5877.660000000001</v>
       </c>
       <c r="F61">
-        <v>6044.608999999999</v>
+        <v>6147.06</v>
       </c>
       <c r="G61">
         <v>495.5</v>
@@ -6295,28 +6295,28 @@
         <v>1477.7</v>
       </c>
       <c r="M61">
-        <v>328.2222687</v>
+        <v>333.785358</v>
       </c>
       <c r="N61">
-        <v>1149.4777313</v>
+        <v>1143.914642</v>
       </c>
       <c r="O61">
-        <v>229.89554626</v>
+        <v>228.7829284</v>
       </c>
       <c r="P61">
-        <v>919.58218504</v>
+        <v>915.1317136</v>
       </c>
       <c r="Q61">
-        <v>1173.18218504</v>
+        <v>1168.7317136</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1965374602731157</v>
+        <v>0.1999555432725061</v>
       </c>
       <c r="T61">
-        <v>2.331860570168059</v>
+        <v>2.38473722708797</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.502132063899174</v>
+        <v>4.427096529500853</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1060462173090025</v>
+        <v>0.1058824759060275</v>
       </c>
       <c r="C62">
-        <v>5248.216912734467</v>
+        <v>5167.573118705846</v>
       </c>
       <c r="D62">
-        <v>10899.77691273447</v>
+        <v>10921.58411870585</v>
       </c>
       <c r="E62">
-        <v>5877.660000000001</v>
+        <v>5980.111000000001</v>
       </c>
       <c r="F62">
-        <v>6147.06</v>
+        <v>6249.511</v>
       </c>
       <c r="G62">
         <v>495.5</v>
@@ -6377,28 +6377,28 @@
         <v>1477.7</v>
       </c>
       <c r="M62">
-        <v>333.785358</v>
+        <v>339.3484473</v>
       </c>
       <c r="N62">
-        <v>1143.914642</v>
+        <v>1138.3515527</v>
       </c>
       <c r="O62">
-        <v>228.7829284</v>
+        <v>227.67031054</v>
       </c>
       <c r="P62">
-        <v>915.1317136</v>
+        <v>910.68124216</v>
       </c>
       <c r="Q62">
-        <v>1168.7317136</v>
+        <v>1164.28124216</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1999555432725061</v>
+        <v>0.2035489125795575</v>
       </c>
       <c r="T62">
-        <v>2.38473722708797</v>
+        <v>2.440325507439671</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.427096529500853</v>
+        <v>4.354521176558216</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1058824759060275</v>
+        <v>0.1057187345030524</v>
       </c>
       <c r="C63">
-        <v>5167.573118705846</v>
+        <v>5087.016759050569</v>
       </c>
       <c r="D63">
-        <v>10921.58411870585</v>
+        <v>10943.47875905057</v>
       </c>
       <c r="E63">
-        <v>5980.111000000001</v>
+        <v>6082.562000000001</v>
       </c>
       <c r="F63">
-        <v>6249.511</v>
+        <v>6351.962</v>
       </c>
       <c r="G63">
         <v>495.5</v>
@@ -6459,28 +6459,28 @@
         <v>1477.7</v>
       </c>
       <c r="M63">
-        <v>339.3484473</v>
+        <v>344.9115366</v>
       </c>
       <c r="N63">
-        <v>1138.3515527</v>
+        <v>1132.7884634</v>
       </c>
       <c r="O63">
-        <v>227.67031054</v>
+        <v>226.55769268</v>
       </c>
       <c r="P63">
-        <v>910.68124216</v>
+        <v>906.23077072</v>
       </c>
       <c r="Q63">
-        <v>1164.28124216</v>
+        <v>1159.83077072</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2035489125795575</v>
+        <v>0.2073314065869801</v>
       </c>
       <c r="T63">
-        <v>2.440325507439671</v>
+        <v>2.498839486757251</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.354521176558216</v>
+        <v>4.284286964033084</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1057187345030524</v>
+        <v>0.1060589931000774</v>
       </c>
       <c r="C64">
-        <v>5087.016759050569</v>
+        <v>4939.166084937888</v>
       </c>
       <c r="D64">
-        <v>10943.47875905057</v>
+        <v>10898.07908493789</v>
       </c>
       <c r="E64">
-        <v>6082.562000000001</v>
+        <v>6185.013000000001</v>
       </c>
       <c r="F64">
-        <v>6351.962</v>
+        <v>6454.413</v>
       </c>
       <c r="G64">
         <v>495.5</v>
@@ -6541,45 +6541,45 @@
         <v>1477.7</v>
       </c>
       <c r="M64">
-        <v>344.9115366</v>
+        <v>356.9290389</v>
       </c>
       <c r="N64">
-        <v>1132.7884634</v>
+        <v>1120.7709611</v>
       </c>
       <c r="O64">
-        <v>226.55769268</v>
+        <v>224.15419222</v>
       </c>
       <c r="P64">
-        <v>906.23077072</v>
+        <v>896.61676888</v>
       </c>
       <c r="Q64">
-        <v>1159.83077072</v>
+        <v>1150.21676888</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2073314065869801</v>
+        <v>0.211318359729939</v>
       </c>
       <c r="T64">
-        <v>2.498839486757251</v>
+        <v>2.560516383875781</v>
       </c>
       <c r="U64">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.284286964033084</v>
+        <v>4.14003860418318</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1060589931000774</v>
+        <v>0.1059032516971024</v>
       </c>
       <c r="C65">
-        <v>4939.166084937888</v>
+        <v>4857.448350679249</v>
       </c>
       <c r="D65">
-        <v>10898.07908493789</v>
+        <v>10918.81235067925</v>
       </c>
       <c r="E65">
-        <v>6185.013000000001</v>
+        <v>6287.464000000001</v>
       </c>
       <c r="F65">
-        <v>6454.413</v>
+        <v>6556.864</v>
       </c>
       <c r="G65">
         <v>495.5</v>
@@ -6623,28 +6623,28 @@
         <v>1477.7</v>
       </c>
       <c r="M65">
-        <v>356.9290389</v>
+        <v>362.5945792000001</v>
       </c>
       <c r="N65">
-        <v>1120.7709611</v>
+        <v>1115.1054208</v>
       </c>
       <c r="O65">
-        <v>224.15419222</v>
+        <v>223.02108416</v>
       </c>
       <c r="P65">
-        <v>896.61676888</v>
+        <v>892.0843366400001</v>
       </c>
       <c r="Q65">
-        <v>1150.21676888</v>
+        <v>1145.68433664</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.211318359729939</v>
+        <v>0.215526810269729</v>
       </c>
       <c r="T65">
-        <v>2.560516383875781</v>
+        <v>2.625619775278674</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.14003860418318</v>
+        <v>4.075350500992817</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1059032516971024</v>
+        <v>0.1057475102941274</v>
       </c>
       <c r="C66">
-        <v>4857.448350679249</v>
+        <v>4775.809655611867</v>
       </c>
       <c r="D66">
-        <v>10918.81235067925</v>
+        <v>10939.62465561187</v>
       </c>
       <c r="E66">
-        <v>6287.464000000001</v>
+        <v>6389.915000000001</v>
       </c>
       <c r="F66">
-        <v>6556.864</v>
+        <v>6659.315000000001</v>
       </c>
       <c r="G66">
         <v>495.5</v>
@@ -6705,28 +6705,28 @@
         <v>1477.7</v>
       </c>
       <c r="M66">
-        <v>362.5945792000001</v>
+        <v>368.2601195</v>
       </c>
       <c r="N66">
-        <v>1115.1054208</v>
+        <v>1109.4398805</v>
       </c>
       <c r="O66">
-        <v>223.02108416</v>
+        <v>221.8879761</v>
       </c>
       <c r="P66">
-        <v>892.0843366400001</v>
+        <v>887.5519044</v>
       </c>
       <c r="Q66">
-        <v>1145.68433664</v>
+        <v>1141.1519044</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.215526810269729</v>
+        <v>0.2199757436975069</v>
       </c>
       <c r="T66">
-        <v>2.625619775278674</v>
+        <v>2.694443360476018</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.075350500992817</v>
+        <v>4.012652800977544</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1057475102941274</v>
+        <v>0.1055917688911524</v>
       </c>
       <c r="C67">
-        <v>4775.809655611867</v>
+        <v>4694.250452567757</v>
       </c>
       <c r="D67">
-        <v>10939.62465561187</v>
+        <v>10960.51645256776</v>
       </c>
       <c r="E67">
-        <v>6389.915000000001</v>
+        <v>6492.366000000001</v>
       </c>
       <c r="F67">
-        <v>6659.315000000001</v>
+        <v>6761.766000000001</v>
       </c>
       <c r="G67">
         <v>495.5</v>
@@ -6787,28 +6787,28 @@
         <v>1477.7</v>
       </c>
       <c r="M67">
-        <v>368.2601195</v>
+        <v>373.9256598000001</v>
       </c>
       <c r="N67">
-        <v>1109.4398805</v>
+        <v>1103.7743402</v>
       </c>
       <c r="O67">
-        <v>221.8879761</v>
+        <v>220.75486804</v>
       </c>
       <c r="P67">
-        <v>887.5519044</v>
+        <v>883.0194721600001</v>
       </c>
       <c r="Q67">
-        <v>1141.1519044</v>
+        <v>1136.61947216</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2199757436975069</v>
+        <v>0.2246863790916248</v>
       </c>
       <c r="T67">
-        <v>2.694443360476018</v>
+        <v>2.767315391861441</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.012652800977544</v>
+        <v>3.951855031265763</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1055917688911524</v>
+        <v>0.1054360274881774</v>
       </c>
       <c r="C68">
-        <v>4694.250452567757</v>
+        <v>4612.771197844697</v>
       </c>
       <c r="D68">
-        <v>10960.51645256776</v>
+        <v>10981.4881978447</v>
       </c>
       <c r="E68">
-        <v>6492.366000000001</v>
+        <v>6594.817000000001</v>
       </c>
       <c r="F68">
-        <v>6761.766000000001</v>
+        <v>6864.217000000001</v>
       </c>
       <c r="G68">
         <v>495.5</v>
@@ -6869,28 +6869,28 @@
         <v>1477.7</v>
       </c>
       <c r="M68">
-        <v>373.9256598000001</v>
+        <v>379.5912001</v>
       </c>
       <c r="N68">
-        <v>1103.7743402</v>
+        <v>1098.1087999</v>
       </c>
       <c r="O68">
-        <v>220.75486804</v>
+        <v>219.62175998</v>
       </c>
       <c r="P68">
-        <v>883.0194721600001</v>
+        <v>878.4870399200001</v>
       </c>
       <c r="Q68">
-        <v>1136.61947216</v>
+        <v>1132.08703992</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2246863790916248</v>
+        <v>0.2296825075399316</v>
       </c>
       <c r="T68">
-        <v>2.767315391861441</v>
+        <v>2.844603909997497</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.951855031265763</v>
+        <v>3.892872120351349</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1054360274881774</v>
+        <v>0.1052802860852024</v>
       </c>
       <c r="C69">
-        <v>4612.771197844697</v>
+        <v>4531.372351239484</v>
       </c>
       <c r="D69">
-        <v>10981.4881978447</v>
+        <v>11002.54035123948</v>
       </c>
       <c r="E69">
-        <v>6594.817000000001</v>
+        <v>6697.268000000001</v>
       </c>
       <c r="F69">
-        <v>6864.217000000001</v>
+        <v>6966.668000000001</v>
       </c>
       <c r="G69">
         <v>495.5</v>
@@ -6951,28 +6951,28 @@
         <v>1477.7</v>
       </c>
       <c r="M69">
-        <v>379.5912001</v>
+        <v>385.2567404000001</v>
       </c>
       <c r="N69">
-        <v>1098.1087999</v>
+        <v>1092.4432596</v>
       </c>
       <c r="O69">
-        <v>219.62175998</v>
+        <v>218.48865192</v>
       </c>
       <c r="P69">
-        <v>878.4870399200001</v>
+        <v>873.95460768</v>
       </c>
       <c r="Q69">
-        <v>1132.08703992</v>
+        <v>1127.55460768</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2296825075399316</v>
+        <v>0.2349908940162575</v>
       </c>
       <c r="T69">
-        <v>2.844603909997497</v>
+        <v>2.926722960517054</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.892872120351349</v>
+        <v>3.835624000934416</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1052802860852024</v>
+        <v>0.1051245446822274</v>
       </c>
       <c r="C70">
-        <v>4531.372351239484</v>
+        <v>4450.054376081487</v>
       </c>
       <c r="D70">
-        <v>11002.54035123948</v>
+        <v>11023.67337608149</v>
       </c>
       <c r="E70">
-        <v>6697.268000000001</v>
+        <v>6799.719000000001</v>
       </c>
       <c r="F70">
-        <v>6966.668000000001</v>
+        <v>7069.119000000001</v>
       </c>
       <c r="G70">
         <v>495.5</v>
@@ -7033,28 +7033,28 @@
         <v>1477.7</v>
       </c>
       <c r="M70">
-        <v>385.2567404000001</v>
+        <v>390.9222807</v>
       </c>
       <c r="N70">
-        <v>1092.4432596</v>
+        <v>1086.7777193</v>
       </c>
       <c r="O70">
-        <v>218.48865192</v>
+        <v>217.35554386</v>
       </c>
       <c r="P70">
-        <v>873.95460768</v>
+        <v>869.4221754399999</v>
       </c>
       <c r="Q70">
-        <v>1127.55460768</v>
+        <v>1123.02217544</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2349908940162575</v>
+        <v>0.2406417570394433</v>
       </c>
       <c r="T70">
-        <v>2.926722960517054</v>
+        <v>3.014140014295939</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.835624000934416</v>
+        <v>3.780035247297686</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1051245446822274</v>
+        <v>0.1049688032792524</v>
       </c>
       <c r="C71">
-        <v>4450.054376081487</v>
+        <v>4368.817739266692</v>
       </c>
       <c r="D71">
-        <v>11023.67337608149</v>
+        <v>11044.88773926669</v>
       </c>
       <c r="E71">
-        <v>6799.719000000001</v>
+        <v>6902.170000000001</v>
       </c>
       <c r="F71">
-        <v>7069.119000000001</v>
+        <v>7171.570000000001</v>
       </c>
       <c r="G71">
         <v>495.5</v>
@@ -7115,28 +7115,28 @@
         <v>1477.7</v>
       </c>
       <c r="M71">
-        <v>390.9222807</v>
+        <v>396.5878210000001</v>
       </c>
       <c r="N71">
-        <v>1086.7777193</v>
+        <v>1081.112179</v>
       </c>
       <c r="O71">
-        <v>217.35554386</v>
+        <v>216.2224358</v>
       </c>
       <c r="P71">
-        <v>869.4221754399999</v>
+        <v>864.8897432</v>
       </c>
       <c r="Q71">
-        <v>1123.02217544</v>
+        <v>1118.4897432</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2406417570394433</v>
+        <v>0.2466693442641747</v>
       </c>
       <c r="T71">
-        <v>3.014140014295939</v>
+        <v>3.107384871660082</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.780035247297686</v>
+        <v>3.726034743764862</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1049688032792524</v>
+        <v>0.1048130618762774</v>
       </c>
       <c r="C72">
-        <v>4368.817739266692</v>
+        <v>4287.662911292053</v>
       </c>
       <c r="D72">
-        <v>11044.88773926669</v>
+        <v>11066.18391129205</v>
       </c>
       <c r="E72">
-        <v>6902.170000000001</v>
+        <v>7004.621000000001</v>
       </c>
       <c r="F72">
-        <v>7171.570000000001</v>
+        <v>7274.021000000001</v>
       </c>
       <c r="G72">
         <v>495.5</v>
@@ -7197,28 +7197,28 @@
         <v>1477.7</v>
       </c>
       <c r="M72">
-        <v>396.5878210000001</v>
+        <v>402.2533613000001</v>
       </c>
       <c r="N72">
-        <v>1081.112179</v>
+        <v>1075.4466387</v>
       </c>
       <c r="O72">
-        <v>216.2224358</v>
+        <v>215.08932774</v>
       </c>
       <c r="P72">
-        <v>864.8897432</v>
+        <v>860.3573109599999</v>
       </c>
       <c r="Q72">
-        <v>1118.4897432</v>
+        <v>1113.95731096</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2466693442641747</v>
+        <v>0.2531126271595773</v>
       </c>
       <c r="T72">
-        <v>3.107384871660082</v>
+        <v>3.207060408842444</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.726034743764862</v>
+        <v>3.673555381176624</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1048130618762774</v>
+        <v>0.1046573204733024</v>
       </c>
       <c r="C73">
-        <v>4287.662911292054</v>
+        <v>4206.590366290289</v>
       </c>
       <c r="D73">
-        <v>11066.18391129205</v>
+        <v>11087.56236629029</v>
       </c>
       <c r="E73">
-        <v>7004.621</v>
+        <v>7107.072</v>
       </c>
       <c r="F73">
-        <v>7274.021</v>
+        <v>7376.472</v>
       </c>
       <c r="G73">
         <v>495.5</v>
@@ -7279,28 +7279,28 @@
         <v>1477.7</v>
       </c>
       <c r="M73">
-        <v>402.2533613</v>
+        <v>407.9189016</v>
       </c>
       <c r="N73">
-        <v>1075.4466387</v>
+        <v>1069.7810984</v>
       </c>
       <c r="O73">
-        <v>215.08932774</v>
+        <v>213.95621968</v>
       </c>
       <c r="P73">
-        <v>860.3573109599999</v>
+        <v>855.82487872</v>
       </c>
       <c r="Q73">
-        <v>1113.95731096</v>
+        <v>1109.42487872</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2531126271595772</v>
+        <v>0.2600161445475085</v>
       </c>
       <c r="T73">
-        <v>3.207060408842442</v>
+        <v>3.313855627252114</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.673555381176625</v>
+        <v>3.622533778660283</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1046573204733024</v>
+        <v>0.1045015790703274</v>
       </c>
       <c r="C74">
-        <v>4206.590366290289</v>
+        <v>4125.600582065056</v>
       </c>
       <c r="D74">
-        <v>11087.56236629029</v>
+        <v>11109.02358206506</v>
       </c>
       <c r="E74">
-        <v>7107.072</v>
+        <v>7209.523</v>
       </c>
       <c r="F74">
-        <v>7376.472</v>
+        <v>7478.923</v>
       </c>
       <c r="G74">
         <v>495.5</v>
@@ -7361,28 +7361,28 @@
         <v>1477.7</v>
       </c>
       <c r="M74">
-        <v>407.9189016</v>
+        <v>413.5844419</v>
       </c>
       <c r="N74">
-        <v>1069.7810984</v>
+        <v>1064.1155581</v>
       </c>
       <c r="O74">
-        <v>213.95621968</v>
+        <v>212.82311162</v>
       </c>
       <c r="P74">
-        <v>855.82487872</v>
+        <v>851.2924464800001</v>
       </c>
       <c r="Q74">
-        <v>1109.42487872</v>
+        <v>1104.89244648</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2600161445475085</v>
+        <v>0.267431033593805</v>
       </c>
       <c r="T74">
-        <v>3.313855627252114</v>
+        <v>3.42856160258102</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.622533778660283</v>
+        <v>3.572910028267676</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1045015790703274</v>
+        <v>0.1043458376673524</v>
       </c>
       <c r="C75">
-        <v>4125.600582065056</v>
+        <v>4044.694040126564</v>
       </c>
       <c r="D75">
-        <v>11109.02358206506</v>
+        <v>11130.56804012656</v>
       </c>
       <c r="E75">
-        <v>7209.523</v>
+        <v>7311.974</v>
       </c>
       <c r="F75">
-        <v>7478.923</v>
+        <v>7581.374</v>
       </c>
       <c r="G75">
         <v>495.5</v>
@@ -7443,28 +7443,28 @@
         <v>1477.7</v>
       </c>
       <c r="M75">
-        <v>413.5844419</v>
+        <v>419.2499822</v>
       </c>
       <c r="N75">
-        <v>1064.1155581</v>
+        <v>1058.4500178</v>
       </c>
       <c r="O75">
-        <v>212.82311162</v>
+        <v>211.69000356</v>
       </c>
       <c r="P75">
-        <v>851.2924464800001</v>
+        <v>846.76001424</v>
       </c>
       <c r="Q75">
-        <v>1104.89244648</v>
+        <v>1100.36001424</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.267431033593805</v>
+        <v>0.275416298720586</v>
       </c>
       <c r="T75">
-        <v>3.42856160258102</v>
+        <v>3.55209111447369</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.572910028267676</v>
+        <v>3.524627460318113</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1043458376673524</v>
+        <v>0.1041900962643774</v>
       </c>
       <c r="C76">
-        <v>4044.694040126564</v>
+        <v>3963.871225727569</v>
       </c>
       <c r="D76">
-        <v>11130.56804012656</v>
+        <v>11152.19622572757</v>
       </c>
       <c r="E76">
-        <v>7311.974</v>
+        <v>7414.425000000001</v>
       </c>
       <c r="F76">
-        <v>7581.374</v>
+        <v>7683.825000000001</v>
       </c>
       <c r="G76">
         <v>495.5</v>
@@ -7525,28 +7525,28 @@
         <v>1477.7</v>
       </c>
       <c r="M76">
-        <v>419.2499822</v>
+        <v>424.9155225000001</v>
       </c>
       <c r="N76">
-        <v>1058.4500178</v>
+        <v>1052.7844775</v>
       </c>
       <c r="O76">
-        <v>211.69000356</v>
+        <v>210.5568955</v>
       </c>
       <c r="P76">
-        <v>846.76001424</v>
+        <v>842.2275819999999</v>
       </c>
       <c r="Q76">
-        <v>1100.36001424</v>
+        <v>1095.827582</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.275416298720586</v>
+        <v>0.2840403850575094</v>
       </c>
       <c r="T76">
-        <v>3.55209111447369</v>
+        <v>3.685502987317772</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.524627460318113</v>
+        <v>3.477632427513871</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1041900962643774</v>
+        <v>0.1040343548614024</v>
       </c>
       <c r="C77">
-        <v>3963.871225727569</v>
+        <v>3883.132627899827</v>
       </c>
       <c r="D77">
-        <v>11152.19622572757</v>
+        <v>11173.90862789983</v>
       </c>
       <c r="E77">
-        <v>7414.425000000001</v>
+        <v>7516.876000000001</v>
       </c>
       <c r="F77">
-        <v>7683.825000000001</v>
+        <v>7786.276000000001</v>
       </c>
       <c r="G77">
         <v>495.5</v>
@@ -7607,28 +7607,28 @@
         <v>1477.7</v>
       </c>
       <c r="M77">
-        <v>424.9155225000001</v>
+        <v>430.5810628</v>
       </c>
       <c r="N77">
-        <v>1052.7844775</v>
+        <v>1047.1189372</v>
       </c>
       <c r="O77">
-        <v>210.5568955</v>
+        <v>209.42378744</v>
       </c>
       <c r="P77">
-        <v>842.2275819999999</v>
+        <v>837.6951497599999</v>
       </c>
       <c r="Q77">
-        <v>1095.827582</v>
+        <v>1091.29514976</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2840403850575094</v>
+        <v>0.2933831452558432</v>
       </c>
       <c r="T77">
-        <v>3.685502987317772</v>
+        <v>3.830032516232194</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.477632427513871</v>
+        <v>3.431874106099215</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1040343548614024</v>
+        <v>0.1038786134584274</v>
       </c>
       <c r="C78">
-        <v>3883.132627899827</v>
+        <v>3802.478739490933</v>
       </c>
       <c r="D78">
-        <v>11173.90862789983</v>
+        <v>11195.70573949093</v>
       </c>
       <c r="E78">
-        <v>7516.876000000001</v>
+        <v>7619.327000000001</v>
       </c>
       <c r="F78">
-        <v>7786.276000000001</v>
+        <v>7888.727000000001</v>
       </c>
       <c r="G78">
         <v>495.5</v>
@@ -7689,28 +7689,28 @@
         <v>1477.7</v>
       </c>
       <c r="M78">
-        <v>430.5810628</v>
+        <v>436.2466031000001</v>
       </c>
       <c r="N78">
-        <v>1047.1189372</v>
+        <v>1041.4533969</v>
       </c>
       <c r="O78">
-        <v>209.42378744</v>
+        <v>208.29067938</v>
       </c>
       <c r="P78">
-        <v>837.6951497599999</v>
+        <v>833.1627175199999</v>
       </c>
       <c r="Q78">
-        <v>1091.29514976</v>
+        <v>1086.76271752</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2933831452558432</v>
+        <v>0.3035383193844668</v>
       </c>
       <c r="T78">
-        <v>3.830032516232194</v>
+        <v>3.98712983026961</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.431874106099215</v>
+        <v>3.38730431251351</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1038786134584274</v>
+        <v>0.1037228720554524</v>
       </c>
       <c r="C79">
-        <v>3802.478739490933</v>
+        <v>3721.910057201619</v>
       </c>
       <c r="D79">
-        <v>11195.70573949093</v>
+        <v>11217.58805720162</v>
       </c>
       <c r="E79">
-        <v>7619.327000000001</v>
+        <v>7721.778000000001</v>
       </c>
       <c r="F79">
-        <v>7888.727000000001</v>
+        <v>7991.178000000001</v>
       </c>
       <c r="G79">
         <v>495.5</v>
@@ -7771,28 +7771,28 @@
         <v>1477.7</v>
       </c>
       <c r="M79">
-        <v>436.2466031000001</v>
+        <v>441.9121434</v>
       </c>
       <c r="N79">
-        <v>1041.4533969</v>
+        <v>1035.7878566</v>
       </c>
       <c r="O79">
-        <v>208.29067938</v>
+        <v>207.15757132</v>
       </c>
       <c r="P79">
-        <v>833.1627175199999</v>
+        <v>828.63028528</v>
       </c>
       <c r="Q79">
-        <v>1086.76271752</v>
+        <v>1082.23028528</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3035383193844668</v>
+        <v>0.3146166911611471</v>
       </c>
       <c r="T79">
-        <v>3.98712983026961</v>
+        <v>4.158508718310427</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.38730431251351</v>
+        <v>3.343877334147953</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1037228720554524</v>
+        <v>0.1035671306524774</v>
       </c>
       <c r="C80">
-        <v>3721.910057201619</v>
+        <v>3641.427081623484</v>
       </c>
       <c r="D80">
-        <v>11217.58805720162</v>
+        <v>11239.55608162348</v>
       </c>
       <c r="E80">
-        <v>7721.778000000001</v>
+        <v>7824.229000000001</v>
       </c>
       <c r="F80">
-        <v>7991.178000000001</v>
+        <v>8093.629000000001</v>
       </c>
       <c r="G80">
         <v>495.5</v>
@@ -7853,28 +7853,28 @@
         <v>1477.7</v>
       </c>
       <c r="M80">
-        <v>441.9121434</v>
+        <v>447.5776837000001</v>
       </c>
       <c r="N80">
-        <v>1035.7878566</v>
+        <v>1030.1223163</v>
       </c>
       <c r="O80">
-        <v>207.15757132</v>
+        <v>206.02446326</v>
       </c>
       <c r="P80">
-        <v>828.63028528</v>
+        <v>824.09785304</v>
       </c>
       <c r="Q80">
-        <v>1082.23028528</v>
+        <v>1077.69785304</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3146166911611471</v>
+        <v>0.3267501459641779</v>
       </c>
       <c r="T80">
-        <v>4.158508718310427</v>
+        <v>4.346209405212275</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.343877334147953</v>
+        <v>3.301549772956207</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1035671306524774</v>
+        <v>0.1034113892495023</v>
       </c>
       <c r="C81">
-        <v>3641.427081623484</v>
+        <v>3561.030317277171</v>
       </c>
       <c r="D81">
-        <v>11239.55608162348</v>
+        <v>11261.61031727717</v>
       </c>
       <c r="E81">
-        <v>7824.229000000001</v>
+        <v>7926.68</v>
       </c>
       <c r="F81">
-        <v>8093.629000000001</v>
+        <v>8196.08</v>
       </c>
       <c r="G81">
         <v>495.5</v>
@@ -7935,28 +7935,28 @@
         <v>1477.7</v>
       </c>
       <c r="M81">
-        <v>447.5776837000001</v>
+        <v>453.243224</v>
       </c>
       <c r="N81">
-        <v>1030.1223163</v>
+        <v>1024.456776</v>
       </c>
       <c r="O81">
-        <v>206.02446326</v>
+        <v>204.8913552</v>
       </c>
       <c r="P81">
-        <v>824.09785304</v>
+        <v>819.5654208</v>
       </c>
       <c r="Q81">
-        <v>1077.69785304</v>
+        <v>1073.1654208</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3267501459641779</v>
+        <v>0.3400969462475117</v>
       </c>
       <c r="T81">
-        <v>4.346209405212275</v>
+        <v>4.552680160804307</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.301549772956207</v>
+        <v>3.260280400794255</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1034113892495023</v>
+        <v>0.1032556478465273</v>
       </c>
       <c r="C82">
-        <v>3561.030317277171</v>
+        <v>3480.720272650973</v>
       </c>
       <c r="D82">
-        <v>11261.61031727717</v>
+        <v>11283.75127265097</v>
       </c>
       <c r="E82">
-        <v>7926.68</v>
+        <v>8029.131000000001</v>
       </c>
       <c r="F82">
-        <v>8196.08</v>
+        <v>8298.531000000001</v>
       </c>
       <c r="G82">
         <v>495.5</v>
@@ -8017,28 +8017,28 @@
         <v>1477.7</v>
       </c>
       <c r="M82">
-        <v>453.243224</v>
+        <v>458.9087643000001</v>
       </c>
       <c r="N82">
-        <v>1024.456776</v>
+        <v>1018.7912357</v>
       </c>
       <c r="O82">
-        <v>204.8913552</v>
+        <v>203.75824714</v>
       </c>
       <c r="P82">
-        <v>819.5654208</v>
+        <v>815.03298856</v>
       </c>
       <c r="Q82">
-        <v>1073.1654208</v>
+        <v>1068.63298856</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3400969462475117</v>
+        <v>0.3548486728764598</v>
       </c>
       <c r="T82">
-        <v>4.552680160804307</v>
+        <v>4.780884680142869</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.260280400794255</v>
+        <v>3.220030025475806</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1032556478465273</v>
+        <v>0.1030999064435523</v>
       </c>
       <c r="C83">
-        <v>3480.720272650973</v>
+        <v>3400.497460239945</v>
       </c>
       <c r="D83">
-        <v>11283.75127265097</v>
+        <v>11305.97946023995</v>
       </c>
       <c r="E83">
-        <v>8029.131000000001</v>
+        <v>8131.582000000002</v>
       </c>
       <c r="F83">
-        <v>8298.531000000001</v>
+        <v>8400.982000000002</v>
       </c>
       <c r="G83">
         <v>495.5</v>
@@ -8099,28 +8099,28 @@
         <v>1477.7</v>
       </c>
       <c r="M83">
-        <v>458.9087643000001</v>
+        <v>464.5743046000001</v>
       </c>
       <c r="N83">
-        <v>1018.7912357</v>
+        <v>1013.1256954</v>
       </c>
       <c r="O83">
-        <v>203.75824714</v>
+        <v>202.62513908</v>
       </c>
       <c r="P83">
-        <v>815.03298856</v>
+        <v>810.50055632</v>
       </c>
       <c r="Q83">
-        <v>1068.63298856</v>
+        <v>1064.10055632</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3548486728764598</v>
+        <v>0.3712394802419574</v>
       </c>
       <c r="T83">
-        <v>4.780884680142869</v>
+        <v>5.034445257185715</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.220030025475806</v>
+        <v>3.18076136662854</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1030999064435523</v>
+        <v>0.1029441650405773</v>
       </c>
       <c r="C84">
-        <v>3400.497460239945</v>
+        <v>3320.362396585411</v>
       </c>
       <c r="D84">
-        <v>11305.97946023995</v>
+        <v>11328.29539658541</v>
       </c>
       <c r="E84">
-        <v>8131.582000000002</v>
+        <v>8234.033000000001</v>
       </c>
       <c r="F84">
-        <v>8400.982000000002</v>
+        <v>8503.433000000001</v>
       </c>
       <c r="G84">
         <v>495.5</v>
@@ -8181,28 +8181,28 @@
         <v>1477.7</v>
       </c>
       <c r="M84">
-        <v>464.5743046000001</v>
+        <v>470.2398449000001</v>
       </c>
       <c r="N84">
-        <v>1013.1256954</v>
+        <v>1007.4601551</v>
       </c>
       <c r="O84">
-        <v>202.62513908</v>
+        <v>201.49203102</v>
       </c>
       <c r="P84">
-        <v>810.50055632</v>
+        <v>805.9681240799999</v>
       </c>
       <c r="Q84">
-        <v>1064.10055632</v>
+        <v>1059.56812408</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3712394802419574</v>
+        <v>0.3895586178857491</v>
       </c>
       <c r="T84">
-        <v>5.034445257185715</v>
+        <v>5.317836490351251</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.18076136662854</v>
+        <v>3.142438940524582</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1029441650405773</v>
+        <v>0.1027884236376023</v>
       </c>
       <c r="C85">
-        <v>3320.362396585411</v>
+        <v>3240.315602315008</v>
       </c>
       <c r="D85">
-        <v>11328.29539658541</v>
+        <v>11350.69960231501</v>
       </c>
       <c r="E85">
-        <v>8234.033000000001</v>
+        <v>8336.484000000002</v>
       </c>
       <c r="F85">
-        <v>8503.433000000001</v>
+        <v>8605.884000000002</v>
       </c>
       <c r="G85">
         <v>495.5</v>
@@ -8263,28 +8263,28 @@
         <v>1477.7</v>
       </c>
       <c r="M85">
-        <v>470.2398449000001</v>
+        <v>475.9053852000001</v>
       </c>
       <c r="N85">
-        <v>1007.4601551</v>
+        <v>1001.7946148</v>
       </c>
       <c r="O85">
-        <v>201.49203102</v>
+        <v>200.35892296</v>
       </c>
       <c r="P85">
-        <v>805.9681240799999</v>
+        <v>801.4356918399999</v>
       </c>
       <c r="Q85">
-        <v>1059.56812408</v>
+        <v>1055.03569184</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3895586178857491</v>
+        <v>0.4101676477350147</v>
       </c>
       <c r="T85">
-        <v>5.317836490351251</v>
+        <v>5.636651627662477</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.142438940524582</v>
+        <v>3.105028953137384</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1027884236376023</v>
+        <v>0.1026326822346273</v>
       </c>
       <c r="C86">
-        <v>3240.31560231501</v>
+        <v>3160.357602183147</v>
       </c>
       <c r="D86">
-        <v>11350.69960231501</v>
+        <v>11373.19260218315</v>
       </c>
       <c r="E86">
-        <v>8336.484</v>
+        <v>8438.935000000001</v>
       </c>
       <c r="F86">
-        <v>8605.884</v>
+        <v>8708.335000000001</v>
       </c>
       <c r="G86">
         <v>495.5</v>
@@ -8345,28 +8345,28 @@
         <v>1477.7</v>
       </c>
       <c r="M86">
-        <v>475.9053852</v>
+        <v>481.5709255</v>
       </c>
       <c r="N86">
-        <v>1001.7946148</v>
+        <v>996.1290745</v>
       </c>
       <c r="O86">
-        <v>200.35892296</v>
+        <v>199.2258149</v>
       </c>
       <c r="P86">
-        <v>801.4356918400001</v>
+        <v>796.9032596</v>
       </c>
       <c r="Q86">
-        <v>1055.03569184</v>
+        <v>1050.5032596</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4101676477350144</v>
+        <v>0.4335245482308487</v>
       </c>
       <c r="T86">
-        <v>5.636651627662474</v>
+        <v>5.99797544994853</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.105028953137385</v>
+        <v>3.068499200747533</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1026326822346273</v>
+        <v>0.1024769408316523</v>
       </c>
       <c r="C87">
-        <v>3160.357602183147</v>
+        <v>3080.488925112</v>
       </c>
       <c r="D87">
-        <v>11373.19260218315</v>
+        <v>11395.774925112</v>
       </c>
       <c r="E87">
-        <v>8438.935000000001</v>
+        <v>8541.386</v>
       </c>
       <c r="F87">
-        <v>8708.335000000001</v>
+        <v>8810.786</v>
       </c>
       <c r="G87">
         <v>495.5</v>
@@ -8427,28 +8427,28 @@
         <v>1477.7</v>
       </c>
       <c r="M87">
-        <v>481.5709255</v>
+        <v>487.2364658</v>
       </c>
       <c r="N87">
-        <v>996.1290745</v>
+        <v>990.4635342</v>
       </c>
       <c r="O87">
-        <v>199.2258149</v>
+        <v>198.09270684</v>
       </c>
       <c r="P87">
-        <v>796.9032596</v>
+        <v>792.37082736</v>
       </c>
       <c r="Q87">
-        <v>1050.5032596</v>
+        <v>1045.97082736</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4335245482308487</v>
+        <v>0.4602181487975165</v>
       </c>
       <c r="T87">
-        <v>5.99797544994853</v>
+        <v>6.410916961132595</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.068499200747533</v>
+        <v>3.032818977483027</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1024769408316523</v>
+        <v>0.1040611994286773</v>
       </c>
       <c r="C88">
-        <v>3080.488925112</v>
+        <v>2752.423113394649</v>
       </c>
       <c r="D88">
-        <v>11395.774925112</v>
+        <v>11170.16011339465</v>
       </c>
       <c r="E88">
-        <v>8541.386</v>
+        <v>8643.837000000001</v>
       </c>
       <c r="F88">
-        <v>8810.786</v>
+        <v>8913.237000000001</v>
       </c>
       <c r="G88">
         <v>495.5</v>
@@ -8509,45 +8509,45 @@
         <v>1477.7</v>
       </c>
       <c r="M88">
-        <v>487.2364658</v>
+        <v>515.1850986000001</v>
       </c>
       <c r="N88">
-        <v>990.4635342</v>
+        <v>962.5149014</v>
       </c>
       <c r="O88">
-        <v>198.09270684</v>
+        <v>192.50298028</v>
       </c>
       <c r="P88">
-        <v>792.37082736</v>
+        <v>770.01192112</v>
       </c>
       <c r="Q88">
-        <v>1045.97082736</v>
+        <v>1023.61192112</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4602181487975165</v>
+        <v>0.4910184571436715</v>
       </c>
       <c r="T88">
-        <v>6.410916961132595</v>
+        <v>6.887387935575745</v>
       </c>
       <c r="U88">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V88">
         <v>0.2</v>
       </c>
       <c r="W88">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.032818977483027</v>
+        <v>2.868289482781247</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1040611994286773</v>
+        <v>0.1039254580257023</v>
       </c>
       <c r="C89">
-        <v>2752.423113394649</v>
+        <v>2668.952573503551</v>
       </c>
       <c r="D89">
-        <v>11170.16011339465</v>
+        <v>11189.14057350355</v>
       </c>
       <c r="E89">
-        <v>8643.837000000001</v>
+        <v>8746.288</v>
       </c>
       <c r="F89">
-        <v>8913.237000000001</v>
+        <v>9015.688</v>
       </c>
       <c r="G89">
         <v>495.5</v>
@@ -8591,28 +8591,28 @@
         <v>1477.7</v>
       </c>
       <c r="M89">
-        <v>515.1850986000001</v>
+        <v>521.1067664000001</v>
       </c>
       <c r="N89">
-        <v>962.5149014</v>
+        <v>956.5932336</v>
       </c>
       <c r="O89">
-        <v>192.50298028</v>
+        <v>191.31864672</v>
       </c>
       <c r="P89">
-        <v>770.01192112</v>
+        <v>765.27458688</v>
       </c>
       <c r="Q89">
-        <v>1023.61192112</v>
+        <v>1018.87458688</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4910184571436715</v>
+        <v>0.5269521502141857</v>
       </c>
       <c r="T89">
-        <v>6.887387935575745</v>
+        <v>7.443270739092755</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.868289482781247</v>
+        <v>2.835695284113278</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1039254580257023</v>
+        <v>0.1037897166227273</v>
       </c>
       <c r="C90">
-        <v>2668.952573503551</v>
+        <v>2585.546647021465</v>
       </c>
       <c r="D90">
-        <v>11189.14057350355</v>
+        <v>11208.18564702147</v>
       </c>
       <c r="E90">
-        <v>8746.288</v>
+        <v>8848.739000000001</v>
       </c>
       <c r="F90">
-        <v>9015.688</v>
+        <v>9118.139000000001</v>
       </c>
       <c r="G90">
         <v>495.5</v>
@@ -8673,28 +8673,28 @@
         <v>1477.7</v>
       </c>
       <c r="M90">
-        <v>521.1067664000001</v>
+        <v>527.0284342000001</v>
       </c>
       <c r="N90">
-        <v>956.5932336</v>
+        <v>950.6715657999999</v>
       </c>
       <c r="O90">
-        <v>191.31864672</v>
+        <v>190.13431316</v>
       </c>
       <c r="P90">
-        <v>765.27458688</v>
+        <v>760.5372526399999</v>
       </c>
       <c r="Q90">
-        <v>1018.87458688</v>
+        <v>1014.13725264</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5269521502141857</v>
+        <v>0.5694192420247934</v>
       </c>
       <c r="T90">
-        <v>7.443270739092755</v>
+        <v>8.10022314324922</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.835695284113278</v>
+        <v>2.803833539347961</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1037897166227273</v>
+        <v>0.1036539752197523</v>
       </c>
       <c r="C91">
-        <v>2585.546647021465</v>
+        <v>2502.205664447023</v>
       </c>
       <c r="D91">
-        <v>11208.18564702147</v>
+        <v>11227.29566444702</v>
       </c>
       <c r="E91">
-        <v>8848.739000000001</v>
+        <v>8951.190000000001</v>
       </c>
       <c r="F91">
-        <v>9118.139000000001</v>
+        <v>9220.59</v>
       </c>
       <c r="G91">
         <v>495.5</v>
@@ -8755,28 +8755,28 @@
         <v>1477.7</v>
       </c>
       <c r="M91">
-        <v>527.0284342000001</v>
+        <v>532.950102</v>
       </c>
       <c r="N91">
-        <v>950.6715657999999</v>
+        <v>944.749898</v>
       </c>
       <c r="O91">
-        <v>190.13431316</v>
+        <v>188.9499796</v>
       </c>
       <c r="P91">
-        <v>760.5372526399999</v>
+        <v>755.7999184</v>
       </c>
       <c r="Q91">
-        <v>1014.13725264</v>
+        <v>1009.3999184</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5694192420247934</v>
+        <v>0.6203797521975229</v>
       </c>
       <c r="T91">
-        <v>8.10022314324922</v>
+        <v>8.888566028236982</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.803833539347961</v>
+        <v>2.772679833355206</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1036539752197523</v>
+        <v>0.1035182338167773</v>
       </c>
       <c r="C92">
-        <v>2502.205664447023</v>
+        <v>2418.929958536735</v>
       </c>
       <c r="D92">
-        <v>11227.29566444702</v>
+        <v>11246.47095853674</v>
       </c>
       <c r="E92">
-        <v>8951.190000000001</v>
+        <v>9053.641000000001</v>
       </c>
       <c r="F92">
-        <v>9220.59</v>
+        <v>9323.041000000001</v>
       </c>
       <c r="G92">
         <v>495.5</v>
@@ -8837,28 +8837,28 @@
         <v>1477.7</v>
       </c>
       <c r="M92">
-        <v>532.950102</v>
+        <v>538.8717698000002</v>
       </c>
       <c r="N92">
-        <v>944.749898</v>
+        <v>938.8282301999999</v>
       </c>
       <c r="O92">
-        <v>188.9499796</v>
+        <v>187.76564604</v>
       </c>
       <c r="P92">
-        <v>755.7999184</v>
+        <v>751.0625841599999</v>
       </c>
       <c r="Q92">
-        <v>1009.3999184</v>
+        <v>1004.66258416</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6203797521975229</v>
+        <v>0.6826648201864143</v>
       </c>
       <c r="T92">
-        <v>8.888566028236982</v>
+        <v>9.852096220999798</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.772679833355206</v>
+        <v>2.742210824197456</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1035182338167773</v>
+        <v>0.1033824924138023</v>
       </c>
       <c r="C93">
-        <v>2418.929958536735</v>
+        <v>2335.719864324266</v>
       </c>
       <c r="D93">
-        <v>11246.47095853674</v>
+        <v>11265.71186432427</v>
       </c>
       <c r="E93">
-        <v>9053.641000000001</v>
+        <v>9156.092000000001</v>
       </c>
       <c r="F93">
-        <v>9323.041000000001</v>
+        <v>9425.492</v>
       </c>
       <c r="G93">
         <v>495.5</v>
@@ -8919,28 +8919,28 @@
         <v>1477.7</v>
       </c>
       <c r="M93">
-        <v>538.8717698000002</v>
+        <v>544.7934376000001</v>
       </c>
       <c r="N93">
-        <v>938.8282301999999</v>
+        <v>932.9065624</v>
       </c>
       <c r="O93">
-        <v>187.76564604</v>
+        <v>186.58131248</v>
       </c>
       <c r="P93">
-        <v>751.0625841599999</v>
+        <v>746.32524992</v>
       </c>
       <c r="Q93">
-        <v>1004.66258416</v>
+        <v>999.9252499199999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6826648201864143</v>
+        <v>0.7605211551725287</v>
       </c>
       <c r="T93">
-        <v>9.852096220999798</v>
+        <v>11.05650896195332</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.742210824197456</v>
+        <v>2.712404184804005</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1033824924138023</v>
+        <v>0.1032467510108273</v>
       </c>
       <c r="C94">
-        <v>2335.719864324266</v>
+        <v>2252.575719139963</v>
       </c>
       <c r="D94">
-        <v>11265.71186432427</v>
+        <v>11285.01871913996</v>
       </c>
       <c r="E94">
-        <v>9156.092000000001</v>
+        <v>9258.543000000001</v>
       </c>
       <c r="F94">
-        <v>9425.492</v>
+        <v>9527.943000000001</v>
       </c>
       <c r="G94">
         <v>495.5</v>
@@ -9001,28 +9001,28 @@
         <v>1477.7</v>
       </c>
       <c r="M94">
-        <v>544.7934376000001</v>
+        <v>550.7151054000001</v>
       </c>
       <c r="N94">
-        <v>932.9065624</v>
+        <v>926.9848946</v>
       </c>
       <c r="O94">
-        <v>186.58131248</v>
+        <v>185.39697892</v>
       </c>
       <c r="P94">
-        <v>746.32524992</v>
+        <v>741.5879156799999</v>
       </c>
       <c r="Q94">
-        <v>999.9252499199999</v>
+        <v>995.1879156799998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7605211551725287</v>
+        <v>0.8606221572975329</v>
       </c>
       <c r="T94">
-        <v>11.05650896195332</v>
+        <v>12.60503962889356</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.712404184804005</v>
+        <v>2.683238548408263</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1032467510108273</v>
+        <v>0.1031110096078523</v>
       </c>
       <c r="C95">
-        <v>2252.575719139963</v>
+        <v>2169.497862630591</v>
       </c>
       <c r="D95">
-        <v>11285.01871913996</v>
+        <v>11304.39186263059</v>
       </c>
       <c r="E95">
-        <v>9258.543000000001</v>
+        <v>9360.994000000001</v>
       </c>
       <c r="F95">
-        <v>9527.943000000001</v>
+        <v>9630.394</v>
       </c>
       <c r="G95">
         <v>495.5</v>
@@ -9083,28 +9083,28 @@
         <v>1477.7</v>
       </c>
       <c r="M95">
-        <v>550.7151054000001</v>
+        <v>556.6367732000001</v>
       </c>
       <c r="N95">
-        <v>926.9848946</v>
+        <v>921.0632267999999</v>
       </c>
       <c r="O95">
-        <v>185.39697892</v>
+        <v>184.21264536</v>
       </c>
       <c r="P95">
-        <v>741.5879156799999</v>
+        <v>736.8505814399999</v>
       </c>
       <c r="Q95">
-        <v>995.1879156799998</v>
+        <v>990.4505814399998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8606221572975329</v>
+        <v>0.9940901601308718</v>
       </c>
       <c r="T95">
-        <v>12.60503962889356</v>
+        <v>14.66974718481389</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.683238548408263</v>
+        <v>2.65469345746775</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1031110096078523</v>
+        <v>0.1029752682048773</v>
       </c>
       <c r="C96">
-        <v>2169.497862630591</v>
+        <v>2086.486636779207</v>
       </c>
       <c r="D96">
-        <v>11304.39186263059</v>
+        <v>11323.83163677921</v>
       </c>
       <c r="E96">
-        <v>9360.994000000001</v>
+        <v>9463.445000000002</v>
       </c>
       <c r="F96">
-        <v>9630.394</v>
+        <v>9732.845000000001</v>
       </c>
       <c r="G96">
         <v>495.5</v>
@@ -9165,28 +9165,28 @@
         <v>1477.7</v>
       </c>
       <c r="M96">
-        <v>556.6367732000001</v>
+        <v>562.5584410000001</v>
       </c>
       <c r="N96">
-        <v>921.0632267999999</v>
+        <v>915.1415589999999</v>
       </c>
       <c r="O96">
-        <v>184.21264536</v>
+        <v>183.0283118</v>
       </c>
       <c r="P96">
-        <v>736.8505814399999</v>
+        <v>732.1132471999999</v>
       </c>
       <c r="Q96">
-        <v>990.4505814399998</v>
+        <v>985.7132471999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9940901601308718</v>
+        <v>1.180945364097547</v>
       </c>
       <c r="T96">
-        <v>14.66974718481389</v>
+        <v>17.56033776310235</v>
       </c>
       <c r="U96">
         <v>0.0578</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.65469345746775</v>
+        <v>2.626749315810195</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1029752682048773</v>
+        <v>0.1028395268019023</v>
       </c>
       <c r="C97">
-        <v>2086.486636779207</v>
+        <v>2003.54238592533</v>
       </c>
       <c r="D97">
-        <v>11323.83163677921</v>
+        <v>11343.33838592533</v>
       </c>
       <c r="E97">
-        <v>9463.445000000002</v>
+        <v>9565.896000000001</v>
       </c>
       <c r="F97">
-        <v>9732.845000000001</v>
+        <v>9835.296</v>
       </c>
       <c r="G97">
         <v>495.5</v>
@@ -9247,28 +9247,28 @@
         <v>1477.7</v>
       </c>
       <c r="M97">
-        <v>562.5584410000001</v>
+        <v>568.4801088</v>
       </c>
       <c r="N97">
-        <v>915.1415589999999</v>
+        <v>909.2198912</v>
       </c>
       <c r="O97">
-        <v>183.0283118</v>
+        <v>181.84397824</v>
       </c>
       <c r="P97">
-        <v>732.1132471999999</v>
+        <v>727.3759129600001</v>
       </c>
       <c r="Q97">
-        <v>985.7132471999998</v>
+        <v>980.97591296</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.180945364097547</v>
+        <v>1.461228170047559</v>
       </c>
       <c r="T97">
-        <v>17.56033776310235</v>
+        <v>21.89622363053504</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.626749315810195</v>
+        <v>2.599387343770506</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1028395268019023</v>
+        <v>0.1027037853989273</v>
       </c>
       <c r="C98">
-        <v>2003.54238592533</v>
+        <v>1920.665456785222</v>
       </c>
       <c r="D98">
-        <v>11343.33838592533</v>
+        <v>11362.91245678522</v>
       </c>
       <c r="E98">
-        <v>9565.896000000001</v>
+        <v>9668.347</v>
       </c>
       <c r="F98">
-        <v>9835.296</v>
+        <v>9937.746999999999</v>
       </c>
       <c r="G98">
         <v>495.5</v>
@@ -9329,28 +9329,28 @@
         <v>1477.7</v>
       </c>
       <c r="M98">
-        <v>568.4801088</v>
+        <v>574.4017766000001</v>
       </c>
       <c r="N98">
-        <v>909.2198912</v>
+        <v>903.2982234</v>
       </c>
       <c r="O98">
-        <v>181.84397824</v>
+        <v>180.65964468</v>
       </c>
       <c r="P98">
-        <v>727.3759129600001</v>
+        <v>722.6385787199999</v>
       </c>
       <c r="Q98">
-        <v>980.97591296</v>
+        <v>976.2385787199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.461228170047555</v>
+        <v>1.92836617996424</v>
       </c>
       <c r="T98">
-        <v>21.89622363053498</v>
+        <v>29.12270007625609</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.599387343770506</v>
+        <v>2.572589536102768</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1027037853989273</v>
+        <v>0.1025680439959522</v>
       </c>
       <c r="C99">
-        <v>1920.665456785222</v>
+        <v>1837.856198472478</v>
       </c>
       <c r="D99">
-        <v>11362.91245678522</v>
+        <v>11382.55419847248</v>
       </c>
       <c r="E99">
-        <v>9668.347</v>
+        <v>9770.798000000001</v>
       </c>
       <c r="F99">
-        <v>9937.746999999999</v>
+        <v>10040.198</v>
       </c>
       <c r="G99">
         <v>495.5</v>
@@ -9411,28 +9411,28 @@
         <v>1477.7</v>
       </c>
       <c r="M99">
-        <v>574.4017766000001</v>
+        <v>580.3234444000001</v>
       </c>
       <c r="N99">
-        <v>903.2982234</v>
+        <v>897.3765556</v>
       </c>
       <c r="O99">
-        <v>180.65964468</v>
+        <v>179.47531112</v>
       </c>
       <c r="P99">
-        <v>722.6385787199999</v>
+        <v>717.9012444799999</v>
       </c>
       <c r="Q99">
-        <v>976.2385787199999</v>
+        <v>971.5012444799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.92836617996424</v>
+        <v>2.862642199797609</v>
       </c>
       <c r="T99">
-        <v>29.12270007625609</v>
+        <v>43.57565296769832</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.572589536102768</v>
+        <v>2.546338622469066</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1025680439959522</v>
+        <v>0.1024323025929772</v>
       </c>
       <c r="C100">
-        <v>1837.856198472478</v>
+        <v>1755.114962518752</v>
       </c>
       <c r="D100">
-        <v>11382.55419847248</v>
+        <v>11402.26396251875</v>
       </c>
       <c r="E100">
-        <v>9770.798000000001</v>
+        <v>9873.249</v>
       </c>
       <c r="F100">
-        <v>10040.198</v>
+        <v>10142.649</v>
       </c>
       <c r="G100">
         <v>495.5</v>
@@ -9493,28 +9493,28 @@
         <v>1477.7</v>
       </c>
       <c r="M100">
-        <v>580.3234444000001</v>
+        <v>586.2451122</v>
       </c>
       <c r="N100">
-        <v>897.3765556</v>
+        <v>891.4548878000001</v>
       </c>
       <c r="O100">
-        <v>179.47531112</v>
+        <v>178.29097756</v>
       </c>
       <c r="P100">
-        <v>717.9012444799999</v>
+        <v>713.1639102400001</v>
       </c>
       <c r="Q100">
-        <v>971.5012444799999</v>
+        <v>966.76391024</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.862642199797609</v>
+        <v>5.665470259297718</v>
       </c>
       <c r="T100">
-        <v>43.57565296769832</v>
+        <v>86.93451164202502</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.546338622469066</v>
+        <v>2.520618030322915</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1024323025929772</v>
-      </c>
-      <c r="C101">
-        <v>1755.114962518752</v>
-      </c>
-      <c r="D101">
-        <v>11402.26396251875</v>
-      </c>
-      <c r="E101">
-        <v>9873.249</v>
-      </c>
-      <c r="F101">
-        <v>10142.649</v>
-      </c>
-      <c r="G101">
-        <v>495.5</v>
-      </c>
-      <c r="H101">
-        <v>9975.700000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1731.3</v>
-      </c>
-      <c r="K101">
-        <v>253.5999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1477.7</v>
-      </c>
-      <c r="M101">
-        <v>586.2451122</v>
-      </c>
-      <c r="N101">
-        <v>891.4548878000001</v>
-      </c>
-      <c r="O101">
-        <v>178.29097756</v>
-      </c>
-      <c r="P101">
-        <v>713.1639102400001</v>
-      </c>
-      <c r="Q101">
-        <v>966.76391024</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.665470259297718</v>
-      </c>
-      <c r="T101">
-        <v>86.93451164202502</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.04624</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.520618030322915</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
